--- a/00 Reference Document/config/KTL metadata.xlsx
+++ b/00 Reference Document/config/KTL metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Metadata_CBM07WI5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Smart Maintanence\TOV1050_Analyzer\00 Reference Document\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9052EF-6D5F-4DF1-A774-F625F032B6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEB2480-0BE7-4CA8-8BDB-3C8BCF06ACBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{40971268-6843-45A4-929F-390CE8EC23ED}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="2" xr2:uid="{A921305F-48E2-4DF9-9960-13141869B4F1}"/>
   </bookViews>
   <sheets>
     <sheet name="threshold" sheetId="3" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="40">
   <si>
     <t>Location Type</t>
   </si>
@@ -302,9 +302,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -342,7 +342,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -448,7 +448,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -590,7 +590,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -8482,7 +8482,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A406477-0BDC-404F-93CF-7E7D1F43F43F}">
-  <dimension ref="A1:D670"/>
+  <dimension ref="A1:D656"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.54296875" customWidth="1"/>
@@ -9085,7 +9085,7 @@
         <v>98.637100000000004</v>
       </c>
       <c r="C50" s="10">
-        <v>97.645899999999997</v>
+        <v>98.645899999999997</v>
       </c>
       <c r="D50" s="4"/>
     </row>
@@ -9805,7 +9805,7 @@
         <v>97.906100000000009</v>
       </c>
       <c r="C110" s="10">
-        <v>97.904899999999998</v>
+        <v>97.906899999999993</v>
       </c>
       <c r="D110" s="4"/>
     </row>
@@ -9814,10 +9814,10 @@
         <v>27</v>
       </c>
       <c r="B111" s="9">
-        <v>97.905000000000001</v>
+        <v>97.906999999999996</v>
       </c>
       <c r="C111" s="9">
-        <v>97.905000000000001</v>
+        <v>97.906999999999996</v>
       </c>
       <c r="D111" s="4"/>
     </row>
@@ -9826,10 +9826,10 @@
         <v>26</v>
       </c>
       <c r="B112" s="10">
-        <v>97.905100000000004</v>
+        <v>97.9071</v>
       </c>
       <c r="C112" s="10">
-        <v>97.906899999999993</v>
+        <v>97.912899999999993</v>
       </c>
       <c r="D112" s="4"/>
     </row>
@@ -9838,10 +9838,10 @@
         <v>27</v>
       </c>
       <c r="B113" s="9">
-        <v>97.906999999999996</v>
+        <v>97.912999999999997</v>
       </c>
       <c r="C113" s="9">
-        <v>97.906999999999996</v>
+        <v>97.912999999999997</v>
       </c>
       <c r="D113" s="4"/>
     </row>
@@ -9850,10 +9850,10 @@
         <v>26</v>
       </c>
       <c r="B114" s="10">
-        <v>97.9071</v>
+        <v>97.9131</v>
       </c>
       <c r="C114" s="10">
-        <v>97.912899999999993</v>
+        <v>97.922899999999998</v>
       </c>
       <c r="D114" s="4"/>
     </row>
@@ -9862,10 +9862,10 @@
         <v>27</v>
       </c>
       <c r="B115" s="9">
-        <v>97.912999999999997</v>
+        <v>97.923000000000002</v>
       </c>
       <c r="C115" s="9">
-        <v>97.912999999999997</v>
+        <v>97.923000000000002</v>
       </c>
       <c r="D115" s="4"/>
     </row>
@@ -9874,10 +9874,10 @@
         <v>26</v>
       </c>
       <c r="B116" s="10">
-        <v>97.9131</v>
+        <v>97.923100000000005</v>
       </c>
       <c r="C116" s="10">
-        <v>97.922899999999998</v>
+        <v>97.932900000000004</v>
       </c>
       <c r="D116" s="4"/>
     </row>
@@ -9886,10 +9886,10 @@
         <v>27</v>
       </c>
       <c r="B117" s="9">
-        <v>97.923000000000002</v>
+        <v>97.933000000000007</v>
       </c>
       <c r="C117" s="9">
-        <v>97.923000000000002</v>
+        <v>97.933000000000007</v>
       </c>
       <c r="D117" s="4"/>
     </row>
@@ -9898,10 +9898,10 @@
         <v>26</v>
       </c>
       <c r="B118" s="10">
-        <v>97.923100000000005</v>
+        <v>97.93310000000001</v>
       </c>
       <c r="C118" s="10">
-        <v>97.932900000000004</v>
+        <v>97.942899999999995</v>
       </c>
       <c r="D118" s="4"/>
     </row>
@@ -9910,10 +9910,10 @@
         <v>27</v>
       </c>
       <c r="B119" s="9">
-        <v>97.933000000000007</v>
+        <v>97.942999999999998</v>
       </c>
       <c r="C119" s="9">
-        <v>97.933000000000007</v>
+        <v>97.942999999999998</v>
       </c>
       <c r="D119" s="4"/>
     </row>
@@ -9922,10 +9922,10 @@
         <v>26</v>
       </c>
       <c r="B120" s="10">
-        <v>97.93310000000001</v>
+        <v>97.943100000000001</v>
       </c>
       <c r="C120" s="10">
-        <v>97.942899999999995</v>
+        <v>97.9529</v>
       </c>
       <c r="D120" s="4"/>
     </row>
@@ -9934,10 +9934,10 @@
         <v>27</v>
       </c>
       <c r="B121" s="9">
-        <v>97.942999999999998</v>
+        <v>97.953000000000003</v>
       </c>
       <c r="C121" s="9">
-        <v>97.942999999999998</v>
+        <v>97.953000000000003</v>
       </c>
       <c r="D121" s="4"/>
     </row>
@@ -9946,10 +9946,10 @@
         <v>26</v>
       </c>
       <c r="B122" s="10">
-        <v>97.943100000000001</v>
+        <v>97.953100000000006</v>
       </c>
       <c r="C122" s="10">
-        <v>97.9529</v>
+        <v>97.962899999999991</v>
       </c>
       <c r="D122" s="4"/>
     </row>
@@ -9958,10 +9958,10 @@
         <v>27</v>
       </c>
       <c r="B123" s="9">
-        <v>97.953000000000003</v>
+        <v>97.962999999999994</v>
       </c>
       <c r="C123" s="9">
-        <v>97.953000000000003</v>
+        <v>97.962999999999994</v>
       </c>
       <c r="D123" s="4"/>
     </row>
@@ -9970,10 +9970,10 @@
         <v>26</v>
       </c>
       <c r="B124" s="10">
-        <v>97.953100000000006</v>
+        <v>97.963099999999997</v>
       </c>
       <c r="C124" s="10">
-        <v>97.962899999999991</v>
+        <v>97.972899999999996</v>
       </c>
       <c r="D124" s="4"/>
     </row>
@@ -9982,10 +9982,10 @@
         <v>27</v>
       </c>
       <c r="B125" s="9">
-        <v>97.962999999999994</v>
+        <v>97.972999999999999</v>
       </c>
       <c r="C125" s="9">
-        <v>97.962999999999994</v>
+        <v>97.972999999999999</v>
       </c>
       <c r="D125" s="4"/>
     </row>
@@ -9994,10 +9994,10 @@
         <v>26</v>
       </c>
       <c r="B126" s="10">
-        <v>97.963099999999997</v>
+        <v>97.973100000000002</v>
       </c>
       <c r="C126" s="10">
-        <v>97.972899999999996</v>
+        <v>97.982900000000001</v>
       </c>
       <c r="D126" s="4"/>
     </row>
@@ -10006,10 +10006,10 @@
         <v>27</v>
       </c>
       <c r="B127" s="9">
-        <v>97.972999999999999</v>
+        <v>97.983000000000004</v>
       </c>
       <c r="C127" s="9">
-        <v>97.972999999999999</v>
+        <v>97.983000000000004</v>
       </c>
       <c r="D127" s="4"/>
     </row>
@@ -10018,10 +10018,10 @@
         <v>26</v>
       </c>
       <c r="B128" s="10">
-        <v>97.973100000000002</v>
+        <v>97.983100000000007</v>
       </c>
       <c r="C128" s="10">
-        <v>97.982900000000001</v>
+        <v>97.992899999999992</v>
       </c>
       <c r="D128" s="4"/>
     </row>
@@ -10030,10 +10030,10 @@
         <v>27</v>
       </c>
       <c r="B129" s="9">
-        <v>97.983000000000004</v>
+        <v>97.992999999999995</v>
       </c>
       <c r="C129" s="9">
-        <v>97.983000000000004</v>
+        <v>97.992999999999995</v>
       </c>
       <c r="D129" s="4"/>
     </row>
@@ -10042,10 +10042,10 @@
         <v>26</v>
       </c>
       <c r="B130" s="10">
-        <v>97.983100000000007</v>
+        <v>97.993099999999998</v>
       </c>
       <c r="C130" s="10">
-        <v>97.992899999999992</v>
+        <v>98.002899999999997</v>
       </c>
       <c r="D130" s="4"/>
     </row>
@@ -10054,10 +10054,10 @@
         <v>27</v>
       </c>
       <c r="B131" s="9">
-        <v>97.992999999999995</v>
+        <v>98.003</v>
       </c>
       <c r="C131" s="9">
-        <v>97.992999999999995</v>
+        <v>98.003</v>
       </c>
       <c r="D131" s="4"/>
     </row>
@@ -10066,10 +10066,10 @@
         <v>26</v>
       </c>
       <c r="B132" s="10">
-        <v>97.993099999999998</v>
+        <v>98.003099999999989</v>
       </c>
       <c r="C132" s="10">
-        <v>98.002899999999997</v>
+        <v>98.012899999999988</v>
       </c>
       <c r="D132" s="4"/>
     </row>
@@ -10078,10 +10078,10 @@
         <v>27</v>
       </c>
       <c r="B133" s="9">
-        <v>98.003</v>
+        <v>98.012999999999991</v>
       </c>
       <c r="C133" s="9">
-        <v>98.003</v>
+        <v>98.012999999999991</v>
       </c>
       <c r="D133" s="4"/>
     </row>
@@ -10090,10 +10090,10 @@
         <v>26</v>
       </c>
       <c r="B134" s="10">
-        <v>98.003100000000003</v>
+        <v>98.013099999999994</v>
       </c>
       <c r="C134" s="10">
-        <v>98.002899999999983</v>
+        <v>98.022899999999993</v>
       </c>
       <c r="D134" s="4"/>
     </row>
@@ -10102,10 +10102,10 @@
         <v>27</v>
       </c>
       <c r="B135" s="9">
-        <v>98.002999999999986</v>
+        <v>98.022999999999996</v>
       </c>
       <c r="C135" s="9">
-        <v>98.002999999999986</v>
+        <v>98.022999999999996</v>
       </c>
       <c r="D135" s="4"/>
     </row>
@@ -10114,10 +10114,10 @@
         <v>26</v>
       </c>
       <c r="B136" s="10">
-        <v>98.003099999999989</v>
+        <v>98.023099999999999</v>
       </c>
       <c r="C136" s="10">
-        <v>98.012899999999988</v>
+        <v>98.032899999999998</v>
       </c>
       <c r="D136" s="4"/>
     </row>
@@ -10126,10 +10126,10 @@
         <v>27</v>
       </c>
       <c r="B137" s="9">
-        <v>98.012999999999991</v>
+        <v>98.033000000000001</v>
       </c>
       <c r="C137" s="9">
-        <v>98.012999999999991</v>
+        <v>98.033000000000001</v>
       </c>
       <c r="D137" s="4"/>
     </row>
@@ -10138,10 +10138,10 @@
         <v>26</v>
       </c>
       <c r="B138" s="10">
-        <v>98.013099999999994</v>
+        <v>98.033100000000005</v>
       </c>
       <c r="C138" s="10">
-        <v>98.022899999999993</v>
+        <v>98.042900000000003</v>
       </c>
       <c r="D138" s="4"/>
     </row>
@@ -10150,10 +10150,10 @@
         <v>27</v>
       </c>
       <c r="B139" s="9">
-        <v>98.022999999999996</v>
+        <v>98.043000000000006</v>
       </c>
       <c r="C139" s="9">
-        <v>98.022999999999996</v>
+        <v>98.043000000000006</v>
       </c>
       <c r="D139" s="4"/>
     </row>
@@ -10162,10 +10162,10 @@
         <v>26</v>
       </c>
       <c r="B140" s="10">
-        <v>98.023099999999999</v>
+        <v>98.04310000000001</v>
       </c>
       <c r="C140" s="10">
-        <v>98.032899999999998</v>
+        <v>98.052900000000008</v>
       </c>
       <c r="D140" s="4"/>
     </row>
@@ -10174,10 +10174,10 @@
         <v>27</v>
       </c>
       <c r="B141" s="9">
-        <v>98.033000000000001</v>
+        <v>98.053000000000011</v>
       </c>
       <c r="C141" s="9">
-        <v>98.033000000000001</v>
+        <v>98.053000000000011</v>
       </c>
       <c r="D141" s="4"/>
     </row>
@@ -10186,10 +10186,10 @@
         <v>26</v>
       </c>
       <c r="B142" s="10">
-        <v>98.033100000000005</v>
+        <v>98.053100000000015</v>
       </c>
       <c r="C142" s="10">
-        <v>98.042900000000003</v>
+        <v>98.062900000000013</v>
       </c>
       <c r="D142" s="4"/>
     </row>
@@ -10198,10 +10198,10 @@
         <v>27</v>
       </c>
       <c r="B143" s="9">
-        <v>98.043000000000006</v>
+        <v>98.063000000000017</v>
       </c>
       <c r="C143" s="9">
-        <v>98.043000000000006</v>
+        <v>98.063000000000017</v>
       </c>
       <c r="D143" s="4"/>
     </row>
@@ -10210,10 +10210,10 @@
         <v>26</v>
       </c>
       <c r="B144" s="10">
-        <v>98.04310000000001</v>
+        <v>98.06310000000002</v>
       </c>
       <c r="C144" s="10">
-        <v>98.052900000000008</v>
+        <v>98.072900000000018</v>
       </c>
       <c r="D144" s="4"/>
     </row>
@@ -10222,10 +10222,10 @@
         <v>27</v>
       </c>
       <c r="B145" s="9">
-        <v>98.053000000000011</v>
+        <v>98.073000000000022</v>
       </c>
       <c r="C145" s="9">
-        <v>98.053000000000011</v>
+        <v>98.073000000000022</v>
       </c>
       <c r="D145" s="4"/>
     </row>
@@ -10234,10 +10234,10 @@
         <v>26</v>
       </c>
       <c r="B146" s="10">
-        <v>98.053100000000015</v>
+        <v>98.073100000000025</v>
       </c>
       <c r="C146" s="10">
-        <v>98.062900000000013</v>
+        <v>98.093899999999991</v>
       </c>
       <c r="D146" s="4"/>
     </row>
@@ -10246,10 +10246,10 @@
         <v>27</v>
       </c>
       <c r="B147" s="9">
-        <v>98.063000000000017</v>
+        <v>98.093999999999994</v>
       </c>
       <c r="C147" s="9">
-        <v>98.063000000000017</v>
+        <v>98.093999999999994</v>
       </c>
       <c r="D147" s="4"/>
     </row>
@@ -10258,10 +10258,10 @@
         <v>26</v>
       </c>
       <c r="B148" s="10">
-        <v>98.06310000000002</v>
+        <v>98.094099999999997</v>
       </c>
       <c r="C148" s="10">
-        <v>98.072900000000018</v>
+        <v>98.103899999999996</v>
       </c>
       <c r="D148" s="4"/>
     </row>
@@ -10270,10 +10270,10 @@
         <v>27</v>
       </c>
       <c r="B149" s="9">
-        <v>98.073000000000022</v>
+        <v>98.103999999999999</v>
       </c>
       <c r="C149" s="9">
-        <v>98.073000000000022</v>
+        <v>98.103999999999999</v>
       </c>
       <c r="D149" s="4"/>
     </row>
@@ -10282,10 +10282,10 @@
         <v>26</v>
       </c>
       <c r="B150" s="10">
-        <v>98.073100000000025</v>
+        <v>98.104100000000003</v>
       </c>
       <c r="C150" s="10">
-        <v>98.093899999999991</v>
+        <v>98.113900000000001</v>
       </c>
       <c r="D150" s="4"/>
     </row>
@@ -10294,10 +10294,10 @@
         <v>27</v>
       </c>
       <c r="B151" s="9">
-        <v>98.093999999999994</v>
+        <v>98.114000000000004</v>
       </c>
       <c r="C151" s="9">
-        <v>98.093999999999994</v>
+        <v>98.114000000000004</v>
       </c>
       <c r="D151" s="4"/>
     </row>
@@ -10306,10 +10306,10 @@
         <v>26</v>
       </c>
       <c r="B152" s="10">
-        <v>98.094099999999997</v>
+        <v>98.114100000000008</v>
       </c>
       <c r="C152" s="10">
-        <v>98.103899999999996</v>
+        <v>98.123899999999992</v>
       </c>
       <c r="D152" s="4"/>
     </row>
@@ -10318,10 +10318,10 @@
         <v>27</v>
       </c>
       <c r="B153" s="9">
-        <v>98.103999999999999</v>
+        <v>98.123999999999995</v>
       </c>
       <c r="C153" s="9">
-        <v>98.103999999999999</v>
+        <v>98.123999999999995</v>
       </c>
       <c r="D153" s="4"/>
     </row>
@@ -10330,10 +10330,10 @@
         <v>26</v>
       </c>
       <c r="B154" s="10">
-        <v>98.104100000000003</v>
+        <v>98.124099999999999</v>
       </c>
       <c r="C154" s="10">
-        <v>98.113900000000001</v>
+        <v>98.133899999999997</v>
       </c>
       <c r="D154" s="4"/>
     </row>
@@ -10342,10 +10342,10 @@
         <v>27</v>
       </c>
       <c r="B155" s="9">
-        <v>98.114000000000004</v>
+        <v>98.134</v>
       </c>
       <c r="C155" s="9">
-        <v>98.114000000000004</v>
+        <v>98.134</v>
       </c>
       <c r="D155" s="4"/>
     </row>
@@ -10354,10 +10354,10 @@
         <v>26</v>
       </c>
       <c r="B156" s="10">
-        <v>98.114100000000008</v>
+        <v>98.134100000000004</v>
       </c>
       <c r="C156" s="10">
-        <v>98.123899999999992</v>
+        <v>98.143900000000002</v>
       </c>
       <c r="D156" s="4"/>
     </row>
@@ -10366,10 +10366,10 @@
         <v>27</v>
       </c>
       <c r="B157" s="9">
-        <v>98.123999999999995</v>
+        <v>98.144000000000005</v>
       </c>
       <c r="C157" s="9">
-        <v>98.123999999999995</v>
+        <v>98.144000000000005</v>
       </c>
       <c r="D157" s="4"/>
     </row>
@@ -10378,10 +10378,10 @@
         <v>26</v>
       </c>
       <c r="B158" s="10">
-        <v>98.124099999999999</v>
+        <v>98.144100000000009</v>
       </c>
       <c r="C158" s="10">
-        <v>98.133899999999997</v>
+        <v>98.153900000000007</v>
       </c>
       <c r="D158" s="4"/>
     </row>
@@ -10390,10 +10390,10 @@
         <v>27</v>
       </c>
       <c r="B159" s="9">
-        <v>98.134</v>
+        <v>98.154000000000011</v>
       </c>
       <c r="C159" s="9">
-        <v>98.134</v>
+        <v>98.154000000000011</v>
       </c>
       <c r="D159" s="4"/>
     </row>
@@ -10402,10 +10402,10 @@
         <v>26</v>
       </c>
       <c r="B160" s="10">
-        <v>98.134100000000004</v>
+        <v>98.154100000000014</v>
       </c>
       <c r="C160" s="10">
-        <v>98.143900000000002</v>
+        <v>98.163900000000012</v>
       </c>
       <c r="D160" s="4"/>
     </row>
@@ -10414,10 +10414,10 @@
         <v>27</v>
       </c>
       <c r="B161" s="9">
-        <v>98.144000000000005</v>
+        <v>98.164000000000016</v>
       </c>
       <c r="C161" s="9">
-        <v>98.144000000000005</v>
+        <v>98.164000000000016</v>
       </c>
       <c r="D161" s="4"/>
     </row>
@@ -10426,10 +10426,10 @@
         <v>26</v>
       </c>
       <c r="B162" s="10">
-        <v>98.144100000000009</v>
+        <v>98.164100000000019</v>
       </c>
       <c r="C162" s="10">
-        <v>98.153900000000007</v>
+        <v>98.173900000000017</v>
       </c>
       <c r="D162" s="4"/>
     </row>
@@ -10438,10 +10438,10 @@
         <v>27</v>
       </c>
       <c r="B163" s="9">
-        <v>98.154000000000011</v>
+        <v>98.174000000000021</v>
       </c>
       <c r="C163" s="9">
-        <v>98.154000000000011</v>
+        <v>98.174000000000021</v>
       </c>
       <c r="D163" s="4"/>
     </row>
@@ -10450,10 +10450,10 @@
         <v>26</v>
       </c>
       <c r="B164" s="10">
-        <v>98.154100000000014</v>
+        <v>98.174100000000024</v>
       </c>
       <c r="C164" s="10">
-        <v>98.163900000000012</v>
+        <v>98.183900000000023</v>
       </c>
       <c r="D164" s="4"/>
     </row>
@@ -10462,10 +10462,10 @@
         <v>27</v>
       </c>
       <c r="B165" s="9">
-        <v>98.164000000000016</v>
+        <v>98.184000000000026</v>
       </c>
       <c r="C165" s="9">
-        <v>98.164000000000016</v>
+        <v>98.184000000000026</v>
       </c>
       <c r="D165" s="4"/>
     </row>
@@ -10474,10 +10474,10 @@
         <v>26</v>
       </c>
       <c r="B166" s="10">
-        <v>98.164100000000019</v>
+        <v>98.184100000000029</v>
       </c>
       <c r="C166" s="10">
-        <v>98.173900000000017</v>
+        <v>98.193900000000028</v>
       </c>
       <c r="D166" s="4"/>
     </row>
@@ -10486,10 +10486,10 @@
         <v>27</v>
       </c>
       <c r="B167" s="9">
-        <v>98.174000000000021</v>
+        <v>98.194000000000031</v>
       </c>
       <c r="C167" s="9">
-        <v>98.174000000000021</v>
+        <v>98.194000000000031</v>
       </c>
       <c r="D167" s="4"/>
     </row>
@@ -10498,10 +10498,10 @@
         <v>26</v>
       </c>
       <c r="B168" s="10">
-        <v>98.174100000000024</v>
+        <v>98.194100000000034</v>
       </c>
       <c r="C168" s="10">
-        <v>98.183900000000023</v>
+        <v>98.203900000000033</v>
       </c>
       <c r="D168" s="4"/>
     </row>
@@ -10510,10 +10510,10 @@
         <v>27</v>
       </c>
       <c r="B169" s="9">
-        <v>98.184000000000026</v>
+        <v>98.204000000000036</v>
       </c>
       <c r="C169" s="9">
-        <v>98.184000000000026</v>
+        <v>98.204000000000036</v>
       </c>
       <c r="D169" s="4"/>
     </row>
@@ -10522,10 +10522,10 @@
         <v>26</v>
       </c>
       <c r="B170" s="10">
-        <v>98.184100000000029</v>
+        <v>98.204100000000039</v>
       </c>
       <c r="C170" s="10">
-        <v>98.193900000000028</v>
+        <v>98.213900000000038</v>
       </c>
       <c r="D170" s="4"/>
     </row>
@@ -10534,10 +10534,10 @@
         <v>27</v>
       </c>
       <c r="B171" s="9">
-        <v>98.194000000000031</v>
+        <v>98.214000000000041</v>
       </c>
       <c r="C171" s="9">
-        <v>98.194000000000031</v>
+        <v>98.214000000000041</v>
       </c>
       <c r="D171" s="4"/>
     </row>
@@ -10546,10 +10546,10 @@
         <v>26</v>
       </c>
       <c r="B172" s="10">
-        <v>98.194100000000034</v>
+        <v>98.214100000000045</v>
       </c>
       <c r="C172" s="10">
-        <v>98.203900000000033</v>
+        <v>98.223900000000043</v>
       </c>
       <c r="D172" s="4"/>
     </row>
@@ -10558,10 +10558,10 @@
         <v>27</v>
       </c>
       <c r="B173" s="9">
-        <v>98.204000000000036</v>
+        <v>98.224000000000046</v>
       </c>
       <c r="C173" s="9">
-        <v>98.204000000000036</v>
+        <v>98.224000000000046</v>
       </c>
       <c r="D173" s="4"/>
     </row>
@@ -10570,10 +10570,10 @@
         <v>26</v>
       </c>
       <c r="B174" s="10">
-        <v>98.204100000000039</v>
+        <v>98.22410000000005</v>
       </c>
       <c r="C174" s="10">
-        <v>98.213900000000038</v>
+        <v>98.233899999999991</v>
       </c>
       <c r="D174" s="4"/>
     </row>
@@ -10582,10 +10582,10 @@
         <v>27</v>
       </c>
       <c r="B175" s="9">
-        <v>98.214000000000041</v>
+        <v>98.233999999999995</v>
       </c>
       <c r="C175" s="9">
-        <v>98.214000000000041</v>
+        <v>98.233999999999995</v>
       </c>
       <c r="D175" s="4"/>
     </row>
@@ -10594,10 +10594,10 @@
         <v>26</v>
       </c>
       <c r="B176" s="10">
-        <v>98.214100000000045</v>
+        <v>98.234099999999998</v>
       </c>
       <c r="C176" s="10">
-        <v>98.223900000000043</v>
+        <v>98.243899999999996</v>
       </c>
       <c r="D176" s="4"/>
     </row>
@@ -10606,10 +10606,10 @@
         <v>27</v>
       </c>
       <c r="B177" s="9">
-        <v>98.224000000000046</v>
+        <v>98.244</v>
       </c>
       <c r="C177" s="9">
-        <v>98.224000000000046</v>
+        <v>98.244</v>
       </c>
       <c r="D177" s="4"/>
     </row>
@@ -10618,10 +10618,10 @@
         <v>26</v>
       </c>
       <c r="B178" s="10">
-        <v>98.22410000000005</v>
+        <v>98.244100000000003</v>
       </c>
       <c r="C178" s="10">
-        <v>98.233899999999991</v>
+        <v>98.253900000000002</v>
       </c>
       <c r="D178" s="4"/>
     </row>
@@ -10630,10 +10630,10 @@
         <v>27</v>
       </c>
       <c r="B179" s="9">
-        <v>98.233999999999995</v>
+        <v>98.254000000000005</v>
       </c>
       <c r="C179" s="9">
-        <v>98.233999999999995</v>
+        <v>98.254000000000005</v>
       </c>
       <c r="D179" s="4"/>
     </row>
@@ -10642,10 +10642,10 @@
         <v>26</v>
       </c>
       <c r="B180" s="10">
-        <v>98.234099999999998</v>
+        <v>98.254100000000008</v>
       </c>
       <c r="C180" s="10">
-        <v>98.243899999999996</v>
+        <v>98.263899999999992</v>
       </c>
       <c r="D180" s="4"/>
     </row>
@@ -10654,10 +10654,10 @@
         <v>27</v>
       </c>
       <c r="B181" s="9">
-        <v>98.244</v>
+        <v>98.263999999999996</v>
       </c>
       <c r="C181" s="9">
-        <v>98.244</v>
+        <v>98.263999999999996</v>
       </c>
       <c r="D181" s="4"/>
     </row>
@@ -10666,10 +10666,10 @@
         <v>26</v>
       </c>
       <c r="B182" s="10">
-        <v>98.244100000000003</v>
+        <v>98.264099999999999</v>
       </c>
       <c r="C182" s="10">
-        <v>98.253900000000002</v>
+        <v>98.273899999999998</v>
       </c>
       <c r="D182" s="4"/>
     </row>
@@ -10678,10 +10678,10 @@
         <v>27</v>
       </c>
       <c r="B183" s="9">
-        <v>98.254000000000005</v>
+        <v>98.274000000000001</v>
       </c>
       <c r="C183" s="9">
-        <v>98.254000000000005</v>
+        <v>98.274000000000001</v>
       </c>
       <c r="D183" s="4"/>
     </row>
@@ -10690,10 +10690,10 @@
         <v>26</v>
       </c>
       <c r="B184" s="10">
-        <v>98.254100000000008</v>
+        <v>98.274100000000004</v>
       </c>
       <c r="C184" s="10">
-        <v>98.263899999999992</v>
+        <v>98.283900000000003</v>
       </c>
       <c r="D184" s="4"/>
     </row>
@@ -10702,10 +10702,10 @@
         <v>27</v>
       </c>
       <c r="B185" s="9">
-        <v>98.263999999999996</v>
+        <v>98.284000000000006</v>
       </c>
       <c r="C185" s="9">
-        <v>98.263999999999996</v>
+        <v>98.284000000000006</v>
       </c>
       <c r="D185" s="4"/>
     </row>
@@ -10714,10 +10714,10 @@
         <v>26</v>
       </c>
       <c r="B186" s="10">
-        <v>98.264099999999999</v>
+        <v>98.284100000000009</v>
       </c>
       <c r="C186" s="10">
-        <v>98.273899999999998</v>
+        <v>98.293899999999994</v>
       </c>
       <c r="D186" s="4"/>
     </row>
@@ -10726,10 +10726,10 @@
         <v>27</v>
       </c>
       <c r="B187" s="9">
-        <v>98.274000000000001</v>
+        <v>98.293999999999997</v>
       </c>
       <c r="C187" s="9">
-        <v>98.274000000000001</v>
+        <v>98.293999999999997</v>
       </c>
       <c r="D187" s="4"/>
     </row>
@@ -10738,10 +10738,10 @@
         <v>26</v>
       </c>
       <c r="B188" s="10">
-        <v>98.274100000000004</v>
+        <v>98.2941</v>
       </c>
       <c r="C188" s="10">
-        <v>98.283900000000003</v>
+        <v>98.303899999999999</v>
       </c>
       <c r="D188" s="4"/>
     </row>
@@ -10750,10 +10750,10 @@
         <v>27</v>
       </c>
       <c r="B189" s="9">
-        <v>98.284000000000006</v>
+        <v>98.304000000000002</v>
       </c>
       <c r="C189" s="9">
-        <v>98.284000000000006</v>
+        <v>98.304000000000002</v>
       </c>
       <c r="D189" s="4"/>
     </row>
@@ -10762,10 +10762,10 @@
         <v>26</v>
       </c>
       <c r="B190" s="10">
-        <v>98.284100000000009</v>
+        <v>98.304100000000005</v>
       </c>
       <c r="C190" s="10">
-        <v>98.293899999999994</v>
+        <v>98.305899999999994</v>
       </c>
       <c r="D190" s="4"/>
     </row>
@@ -10774,10 +10774,10 @@
         <v>27</v>
       </c>
       <c r="B191" s="9">
-        <v>98.293999999999997</v>
+        <v>98.305999999999997</v>
       </c>
       <c r="C191" s="9">
-        <v>98.293999999999997</v>
+        <v>98.305999999999997</v>
       </c>
       <c r="D191" s="4"/>
     </row>
@@ -10786,10 +10786,10 @@
         <v>26</v>
       </c>
       <c r="B192" s="10">
-        <v>98.2941</v>
+        <v>98.306100000000001</v>
       </c>
       <c r="C192" s="10">
-        <v>98.303899999999999</v>
+        <v>98.306899999999999</v>
       </c>
       <c r="D192" s="4"/>
     </row>
@@ -10798,10 +10798,10 @@
         <v>27</v>
       </c>
       <c r="B193" s="9">
-        <v>98.304000000000002</v>
+        <v>98.307000000000002</v>
       </c>
       <c r="C193" s="9">
-        <v>98.304000000000002</v>
+        <v>98.307000000000002</v>
       </c>
       <c r="D193" s="4"/>
     </row>
@@ -10810,10 +10810,10 @@
         <v>26</v>
       </c>
       <c r="B194" s="10">
-        <v>98.304100000000005</v>
+        <v>98.307100000000005</v>
       </c>
       <c r="C194" s="10">
-        <v>98.305899999999994</v>
+        <v>98.308899999999994</v>
       </c>
       <c r="D194" s="4"/>
     </row>
@@ -10822,10 +10822,10 @@
         <v>27</v>
       </c>
       <c r="B195" s="9">
-        <v>98.305999999999997</v>
+        <v>98.308999999999997</v>
       </c>
       <c r="C195" s="9">
-        <v>98.305999999999997</v>
+        <v>98.308999999999997</v>
       </c>
       <c r="D195" s="4"/>
     </row>
@@ -10834,10 +10834,10 @@
         <v>26</v>
       </c>
       <c r="B196" s="10">
-        <v>98.306100000000001</v>
+        <v>98.309100000000001</v>
       </c>
       <c r="C196" s="10">
-        <v>98.304900000000004</v>
+        <v>98.314899999999994</v>
       </c>
       <c r="D196" s="4"/>
     </row>
@@ -10846,10 +10846,10 @@
         <v>27</v>
       </c>
       <c r="B197" s="9">
-        <v>98.305000000000007</v>
+        <v>98.314999999999998</v>
       </c>
       <c r="C197" s="9">
-        <v>98.305000000000007</v>
+        <v>98.314999999999998</v>
       </c>
       <c r="D197" s="4"/>
     </row>
@@ -10858,10 +10858,10 @@
         <v>26</v>
       </c>
       <c r="B198" s="10">
-        <v>98.30510000000001</v>
+        <v>98.315100000000001</v>
       </c>
       <c r="C198" s="10">
-        <v>98.306899999999999</v>
+        <v>98.32589999999999</v>
       </c>
       <c r="D198" s="4"/>
     </row>
@@ -10870,10 +10870,10 @@
         <v>27</v>
       </c>
       <c r="B199" s="9">
-        <v>98.307000000000002</v>
+        <v>98.325999999999993</v>
       </c>
       <c r="C199" s="9">
-        <v>98.307000000000002</v>
+        <v>98.325999999999993</v>
       </c>
       <c r="D199" s="4"/>
     </row>
@@ -10882,10 +10882,10 @@
         <v>26</v>
       </c>
       <c r="B200" s="10">
-        <v>98.307100000000005</v>
+        <v>98.326099999999997</v>
       </c>
       <c r="C200" s="10">
-        <v>98.314899999999994</v>
+        <v>98.329899999999995</v>
       </c>
       <c r="D200" s="4"/>
     </row>
@@ -10894,10 +10894,10 @@
         <v>27</v>
       </c>
       <c r="B201" s="9">
-        <v>98.314999999999998</v>
+        <v>98.33</v>
       </c>
       <c r="C201" s="9">
-        <v>98.314999999999998</v>
+        <v>98.33</v>
       </c>
       <c r="D201" s="4"/>
     </row>
@@ -10906,10 +10906,10 @@
         <v>26</v>
       </c>
       <c r="B202" s="10">
-        <v>98.315100000000001</v>
+        <v>98.330100000000002</v>
       </c>
       <c r="C202" s="10">
-        <v>98.32589999999999</v>
+        <v>98.3309</v>
       </c>
       <c r="D202" s="4"/>
     </row>
@@ -10918,10 +10918,10 @@
         <v>27</v>
       </c>
       <c r="B203" s="9">
-        <v>98.325999999999993</v>
+        <v>98.331000000000003</v>
       </c>
       <c r="C203" s="9">
-        <v>98.325999999999993</v>
+        <v>98.331000000000003</v>
       </c>
       <c r="D203" s="4"/>
     </row>
@@ -10930,7 +10930,7 @@
         <v>26</v>
       </c>
       <c r="B204" s="10">
-        <v>98.326099999999997</v>
+        <v>98.331100000000006</v>
       </c>
       <c r="C204" s="10">
         <v>98.335899999999995</v>
@@ -10956,8 +10956,8 @@
       <c r="B206" s="10">
         <v>98.336100000000002</v>
       </c>
-      <c r="C206" s="10">
-        <v>98.3459</v>
+      <c r="C206" s="9">
+        <v>98.341899999999995</v>
       </c>
       <c r="D206" s="4"/>
     </row>
@@ -10966,10 +10966,10 @@
         <v>27</v>
       </c>
       <c r="B207" s="9">
-        <v>98.346000000000004</v>
+        <v>98.341999999999999</v>
       </c>
       <c r="C207" s="9">
-        <v>98.346000000000004</v>
+        <v>98.341999999999999</v>
       </c>
       <c r="D207" s="4"/>
     </row>
@@ -10977,11 +10977,11 @@
       <c r="A208" t="s">
         <v>26</v>
       </c>
-      <c r="B208" s="10">
-        <v>98.346100000000007</v>
+      <c r="B208" s="9">
+        <v>98.342100000000002</v>
       </c>
       <c r="C208" s="10">
-        <v>98.355900000000005</v>
+        <v>98.3459</v>
       </c>
       <c r="D208" s="4"/>
     </row>
@@ -10990,10 +10990,10 @@
         <v>27</v>
       </c>
       <c r="B209" s="9">
-        <v>98.356000000000009</v>
+        <v>98.346000000000004</v>
       </c>
       <c r="C209" s="9">
-        <v>98.356000000000009</v>
+        <v>98.346000000000004</v>
       </c>
       <c r="D209" s="4"/>
     </row>
@@ -11002,10 +11002,10 @@
         <v>26</v>
       </c>
       <c r="B210" s="10">
-        <v>98.356100000000012</v>
-      </c>
-      <c r="C210" s="10">
-        <v>98.365900000000011</v>
+        <v>98.346100000000007</v>
+      </c>
+      <c r="C210" s="9">
+        <v>98.3489</v>
       </c>
       <c r="D210" s="4"/>
     </row>
@@ -11014,10 +11014,10 @@
         <v>27</v>
       </c>
       <c r="B211" s="9">
-        <v>98.366000000000014</v>
+        <v>98.349000000000004</v>
       </c>
       <c r="C211" s="9">
-        <v>98.366000000000014</v>
+        <v>98.349000000000004</v>
       </c>
       <c r="D211" s="4"/>
     </row>
@@ -11025,11 +11025,11 @@
       <c r="A212" t="s">
         <v>26</v>
       </c>
-      <c r="B212" s="10">
-        <v>98.366100000000017</v>
+      <c r="B212" s="9">
+        <v>98.349100000000007</v>
       </c>
       <c r="C212" s="10">
-        <v>98.375900000000016</v>
+        <v>98.355900000000005</v>
       </c>
       <c r="D212" s="4"/>
     </row>
@@ -11038,10 +11038,10 @@
         <v>27</v>
       </c>
       <c r="B213" s="9">
-        <v>98.376000000000019</v>
+        <v>98.356000000000009</v>
       </c>
       <c r="C213" s="9">
-        <v>98.376000000000019</v>
+        <v>98.356000000000009</v>
       </c>
       <c r="D213" s="4"/>
     </row>
@@ -11050,10 +11050,10 @@
         <v>26</v>
       </c>
       <c r="B214" s="10">
-        <v>98.376100000000022</v>
+        <v>98.356100000000012</v>
       </c>
       <c r="C214" s="10">
-        <v>98.385900000000021</v>
+        <v>98.365900000000011</v>
       </c>
       <c r="D214" s="4"/>
     </row>
@@ -11062,10 +11062,10 @@
         <v>27</v>
       </c>
       <c r="B215" s="9">
-        <v>98.386000000000024</v>
+        <v>98.366000000000014</v>
       </c>
       <c r="C215" s="9">
-        <v>98.386000000000024</v>
+        <v>98.366000000000014</v>
       </c>
       <c r="D215" s="4"/>
     </row>
@@ -11074,10 +11074,10 @@
         <v>26</v>
       </c>
       <c r="B216" s="10">
-        <v>98.386100000000027</v>
-      </c>
-      <c r="C216" s="10">
-        <v>98.395900000000026</v>
+        <v>98.366100000000017</v>
+      </c>
+      <c r="C216" s="9">
+        <v>98.367900000000006</v>
       </c>
       <c r="D216" s="4"/>
     </row>
@@ -11086,10 +11086,10 @@
         <v>27</v>
       </c>
       <c r="B217" s="9">
-        <v>98.396000000000029</v>
+        <v>98.367999999999995</v>
       </c>
       <c r="C217" s="9">
-        <v>98.396000000000029</v>
+        <v>98.367999999999995</v>
       </c>
       <c r="D217" s="4"/>
     </row>
@@ -11097,11 +11097,11 @@
       <c r="A218" t="s">
         <v>26</v>
       </c>
-      <c r="B218" s="10">
-        <v>98.396100000000033</v>
+      <c r="B218" s="9">
+        <v>98.368099999999998</v>
       </c>
       <c r="C218" s="10">
-        <v>98.405900000000031</v>
+        <v>98.370900000000006</v>
       </c>
       <c r="D218" s="4"/>
     </row>
@@ -11110,10 +11110,10 @@
         <v>27</v>
       </c>
       <c r="B219" s="9">
-        <v>98.406000000000034</v>
+        <v>98.370999999999995</v>
       </c>
       <c r="C219" s="9">
-        <v>98.406000000000034</v>
+        <v>98.370999999999995</v>
       </c>
       <c r="D219" s="4"/>
     </row>
@@ -11122,10 +11122,10 @@
         <v>26</v>
       </c>
       <c r="B220" s="10">
-        <v>98.406100000000038</v>
+        <v>98.371099999999998</v>
       </c>
       <c r="C220" s="10">
-        <v>98.415900000000036</v>
+        <v>98.374899999999997</v>
       </c>
       <c r="D220" s="4"/>
     </row>
@@ -11134,10 +11134,10 @@
         <v>27</v>
       </c>
       <c r="B221" s="9">
-        <v>98.416000000000039</v>
+        <v>98.375</v>
       </c>
       <c r="C221" s="9">
-        <v>98.416000000000039</v>
+        <v>98.375</v>
       </c>
       <c r="D221" s="4"/>
     </row>
@@ -11146,10 +11146,10 @@
         <v>26</v>
       </c>
       <c r="B222" s="10">
-        <v>98.416100000000043</v>
+        <v>98.375100000000003</v>
       </c>
       <c r="C222" s="10">
-        <v>98.425900000000041</v>
+        <v>98.375900000000001</v>
       </c>
       <c r="D222" s="4"/>
     </row>
@@ -11158,10 +11158,10 @@
         <v>27</v>
       </c>
       <c r="B223" s="9">
-        <v>98.426000000000045</v>
+        <v>98.376000000000019</v>
       </c>
       <c r="C223" s="9">
-        <v>98.426000000000045</v>
+        <v>98.376000000000019</v>
       </c>
       <c r="D223" s="4"/>
     </row>
@@ -11169,11 +11169,11 @@
       <c r="A224" t="s">
         <v>26</v>
       </c>
-      <c r="B224" s="10">
-        <v>98.426100000000048</v>
-      </c>
-      <c r="C224" s="10">
-        <v>98.435900000000046</v>
+      <c r="B224" s="9">
+        <v>98.376099999999994</v>
+      </c>
+      <c r="C224" s="9">
+        <v>98.377899999999997</v>
       </c>
       <c r="D224" s="4"/>
     </row>
@@ -11182,10 +11182,10 @@
         <v>27</v>
       </c>
       <c r="B225" s="9">
-        <v>98.43600000000005</v>
+        <v>98.378</v>
       </c>
       <c r="C225" s="9">
-        <v>98.43600000000005</v>
+        <v>98.378</v>
       </c>
       <c r="D225" s="4"/>
     </row>
@@ -11194,10 +11194,10 @@
         <v>26</v>
       </c>
       <c r="B226" s="10">
-        <v>98.436100000000053</v>
+        <v>98.378100000000003</v>
       </c>
       <c r="C226" s="10">
-        <v>98.445900000000051</v>
+        <v>98.381900000000002</v>
       </c>
       <c r="D226" s="4"/>
     </row>
@@ -11206,10 +11206,10 @@
         <v>27</v>
       </c>
       <c r="B227" s="9">
-        <v>98.446000000000055</v>
+        <v>98.382000000000005</v>
       </c>
       <c r="C227" s="9">
-        <v>98.446000000000055</v>
+        <v>98.382000000000005</v>
       </c>
       <c r="D227" s="4"/>
     </row>
@@ -11217,11 +11217,11 @@
       <c r="A228" t="s">
         <v>26</v>
       </c>
-      <c r="B228" s="10">
-        <v>98.446100000000058</v>
-      </c>
-      <c r="C228" s="10">
-        <v>98.4559</v>
+      <c r="B228" s="9">
+        <v>98.382099999999994</v>
+      </c>
+      <c r="C228" s="9">
+        <v>98.385900000000007</v>
       </c>
       <c r="D228" s="4"/>
     </row>
@@ -11230,10 +11230,10 @@
         <v>27</v>
       </c>
       <c r="B229" s="9">
-        <v>98.456000000000003</v>
+        <v>98.386000000000024</v>
       </c>
       <c r="C229" s="9">
-        <v>98.456000000000003</v>
+        <v>98.386000000000024</v>
       </c>
       <c r="D229" s="4"/>
     </row>
@@ -11241,11 +11241,11 @@
       <c r="A230" t="s">
         <v>26</v>
       </c>
-      <c r="B230" s="10">
-        <v>98.456100000000006</v>
-      </c>
-      <c r="C230" s="10">
-        <v>98.465899999999991</v>
+      <c r="B230" s="9">
+        <v>98.386099999999999</v>
+      </c>
+      <c r="C230" s="9">
+        <v>98.387900000000002</v>
       </c>
       <c r="D230" s="4"/>
     </row>
@@ -11254,10 +11254,10 @@
         <v>27</v>
       </c>
       <c r="B231" s="9">
-        <v>98.465999999999994</v>
+        <v>98.388000000000005</v>
       </c>
       <c r="C231" s="9">
-        <v>98.465999999999994</v>
+        <v>98.388000000000005</v>
       </c>
       <c r="D231" s="4"/>
     </row>
@@ -11266,10 +11266,10 @@
         <v>26</v>
       </c>
       <c r="B232" s="10">
-        <v>98.466099999999997</v>
+        <v>98.388099999999994</v>
       </c>
       <c r="C232" s="10">
-        <v>98.475899999999996</v>
+        <v>98.389899999999997</v>
       </c>
       <c r="D232" s="4"/>
     </row>
@@ -11278,10 +11278,10 @@
         <v>27</v>
       </c>
       <c r="B233" s="9">
-        <v>98.475999999999999</v>
+        <v>98.39</v>
       </c>
       <c r="C233" s="9">
-        <v>98.475999999999999</v>
+        <v>98.39</v>
       </c>
       <c r="D233" s="4"/>
     </row>
@@ -11289,11 +11289,11 @@
       <c r="A234" t="s">
         <v>26</v>
       </c>
-      <c r="B234" s="10">
-        <v>98.476100000000002</v>
-      </c>
-      <c r="C234" s="10">
-        <v>98.484899999999996</v>
+      <c r="B234" s="9">
+        <v>98.390100000000004</v>
+      </c>
+      <c r="C234" s="9">
+        <v>98.395899999999997</v>
       </c>
       <c r="D234" s="4"/>
     </row>
@@ -11302,10 +11302,10 @@
         <v>27</v>
       </c>
       <c r="B235" s="9">
-        <v>98.484999999999999</v>
+        <v>98.396000000000029</v>
       </c>
       <c r="C235" s="9">
-        <v>98.484999999999999</v>
+        <v>98.396000000000029</v>
       </c>
       <c r="D235" s="4"/>
     </row>
@@ -11314,10 +11314,10 @@
         <v>26</v>
       </c>
       <c r="B236" s="10">
-        <v>98.485100000000003</v>
+        <v>98.396100000000033</v>
       </c>
       <c r="C236" s="10">
-        <v>98.486899999999991</v>
+        <v>98.399900000000002</v>
       </c>
       <c r="D236" s="4"/>
     </row>
@@ -11326,10 +11326,10 @@
         <v>27</v>
       </c>
       <c r="B237" s="9">
-        <v>98.486999999999995</v>
+        <v>98.4</v>
       </c>
       <c r="C237" s="9">
-        <v>98.486999999999995</v>
+        <v>98.4</v>
       </c>
       <c r="D237" s="4"/>
     </row>
@@ -11337,11 +11337,11 @@
       <c r="A238" t="s">
         <v>26</v>
       </c>
-      <c r="B238" s="10">
-        <v>98.487099999999998</v>
-      </c>
-      <c r="C238" s="10">
-        <v>98.488900000000001</v>
+      <c r="B238" s="9">
+        <v>98.400099999999995</v>
+      </c>
+      <c r="C238" s="9">
+        <v>98.402900000000002</v>
       </c>
       <c r="D238" s="4"/>
     </row>
@@ -11350,10 +11350,10 @@
         <v>27</v>
       </c>
       <c r="B239" s="9">
-        <v>98.489000000000004</v>
+        <v>98.403000000000006</v>
       </c>
       <c r="C239" s="9">
-        <v>98.489000000000004</v>
+        <v>98.403000000000006</v>
       </c>
       <c r="D239" s="4"/>
     </row>
@@ -11361,11 +11361,11 @@
       <c r="A240" t="s">
         <v>26</v>
       </c>
-      <c r="B240" s="10">
-        <v>98.489100000000008</v>
-      </c>
-      <c r="C240" s="10">
-        <v>98.487899999999996</v>
+      <c r="B240" s="9">
+        <v>98.403099999999995</v>
+      </c>
+      <c r="C240" s="9">
+        <v>98.405900000000003</v>
       </c>
       <c r="D240" s="4"/>
     </row>
@@ -11374,10 +11374,10 @@
         <v>27</v>
       </c>
       <c r="B241" s="9">
-        <v>98.488</v>
+        <v>98.406000000000034</v>
       </c>
       <c r="C241" s="9">
-        <v>98.488</v>
+        <v>98.406000000000034</v>
       </c>
       <c r="D241" s="4"/>
     </row>
@@ -11385,11 +11385,11 @@
       <c r="A242" t="s">
         <v>26</v>
       </c>
-      <c r="B242" s="10">
-        <v>98.488100000000003</v>
-      </c>
-      <c r="C242" s="10">
-        <v>98.489899999999992</v>
+      <c r="B242" s="9">
+        <v>98.406099999999995</v>
+      </c>
+      <c r="C242" s="9">
+        <v>98.406899999999993</v>
       </c>
       <c r="D242" s="4"/>
     </row>
@@ -11398,10 +11398,10 @@
         <v>27</v>
       </c>
       <c r="B243" s="9">
-        <v>98.49</v>
+        <v>98.406999999999996</v>
       </c>
       <c r="C243" s="9">
-        <v>98.49</v>
+        <v>98.406999999999996</v>
       </c>
       <c r="D243" s="4"/>
     </row>
@@ -11410,10 +11410,10 @@
         <v>26</v>
       </c>
       <c r="B244" s="10">
-        <v>98.490099999999998</v>
+        <v>98.4071</v>
       </c>
       <c r="C244" s="10">
-        <v>98.499899999999997</v>
+        <v>98.410899999999998</v>
       </c>
       <c r="D244" s="4"/>
     </row>
@@ -11422,10 +11422,10 @@
         <v>27</v>
       </c>
       <c r="B245" s="9">
-        <v>98.5</v>
+        <v>98.411000000000001</v>
       </c>
       <c r="C245" s="9">
-        <v>98.5</v>
+        <v>98.411000000000001</v>
       </c>
       <c r="D245" s="4"/>
     </row>
@@ -11433,11 +11433,11 @@
       <c r="A246" t="s">
         <v>26</v>
       </c>
-      <c r="B246" s="10">
-        <v>98.500100000000003</v>
-      </c>
-      <c r="C246" s="10">
-        <v>98.509900000000002</v>
+      <c r="B246" s="9">
+        <v>98.411100000000005</v>
+      </c>
+      <c r="C246" s="9">
+        <v>98.415899999999993</v>
       </c>
       <c r="D246" s="4"/>
     </row>
@@ -11446,10 +11446,10 @@
         <v>27</v>
       </c>
       <c r="B247" s="9">
-        <v>98.51</v>
+        <v>98.416000000000039</v>
       </c>
       <c r="C247" s="9">
-        <v>98.51</v>
+        <v>98.416000000000039</v>
       </c>
       <c r="D247" s="4"/>
     </row>
@@ -11458,10 +11458,10 @@
         <v>26</v>
       </c>
       <c r="B248" s="10">
-        <v>98.510100000000008</v>
+        <v>98.416100000000043</v>
       </c>
       <c r="C248" s="10">
-        <v>98.519900000000007</v>
+        <v>98.418899999999994</v>
       </c>
       <c r="D248" s="4"/>
     </row>
@@ -11470,10 +11470,10 @@
         <v>27</v>
       </c>
       <c r="B249" s="9">
-        <v>98.52000000000001</v>
+        <v>98.418999999999997</v>
       </c>
       <c r="C249" s="9">
-        <v>98.52000000000001</v>
+        <v>98.418999999999997</v>
       </c>
       <c r="D249" s="4"/>
     </row>
@@ -11481,11 +11481,11 @@
       <c r="A250" t="s">
         <v>26</v>
       </c>
-      <c r="B250" s="10">
-        <v>98.520100000000014</v>
-      </c>
-      <c r="C250" s="10">
-        <v>98.529900000000012</v>
+      <c r="B250" s="9">
+        <v>98.4191</v>
+      </c>
+      <c r="C250" s="9">
+        <v>98.425899999999999</v>
       </c>
       <c r="D250" s="4"/>
     </row>
@@ -11494,10 +11494,10 @@
         <v>27</v>
       </c>
       <c r="B251" s="9">
-        <v>98.530000000000015</v>
+        <v>98.426000000000045</v>
       </c>
       <c r="C251" s="9">
-        <v>98.530000000000015</v>
+        <v>98.426000000000045</v>
       </c>
       <c r="D251" s="4"/>
     </row>
@@ -11506,10 +11506,10 @@
         <v>26</v>
       </c>
       <c r="B252" s="10">
-        <v>98.530100000000019</v>
+        <v>98.426100000000048</v>
       </c>
       <c r="C252" s="10">
-        <v>98.538899999999998</v>
+        <v>98.435900000000046</v>
       </c>
       <c r="D252" s="4"/>
     </row>
@@ -11518,10 +11518,10 @@
         <v>27</v>
       </c>
       <c r="B253" s="9">
-        <v>98.539000000000001</v>
+        <v>98.429000000000002</v>
       </c>
       <c r="C253" s="9">
-        <v>98.539000000000001</v>
+        <v>98.429000000000002</v>
       </c>
       <c r="D253" s="4"/>
     </row>
@@ -11529,11 +11529,11 @@
       <c r="A254" t="s">
         <v>26</v>
       </c>
-      <c r="B254" s="10">
-        <v>98.539100000000005</v>
-      </c>
-      <c r="C254" s="10">
-        <v>98.548900000000003</v>
+      <c r="B254" s="9">
+        <v>98.429100000000005</v>
+      </c>
+      <c r="C254" s="9">
+        <v>98.435900000000004</v>
       </c>
       <c r="D254" s="4"/>
     </row>
@@ -11542,10 +11542,10 @@
         <v>27</v>
       </c>
       <c r="B255" s="9">
-        <v>98.549000000000007</v>
+        <v>98.43600000000005</v>
       </c>
       <c r="C255" s="9">
-        <v>98.549000000000007</v>
+        <v>98.43600000000005</v>
       </c>
       <c r="D255" s="4"/>
     </row>
@@ -11554,10 +11554,10 @@
         <v>26</v>
       </c>
       <c r="B256" s="10">
-        <v>98.54910000000001</v>
+        <v>98.436100000000053</v>
       </c>
       <c r="C256" s="10">
-        <v>98.558899999999994</v>
+        <v>98.436899999999994</v>
       </c>
       <c r="D256" s="4"/>
     </row>
@@ -11566,10 +11566,10 @@
         <v>27</v>
       </c>
       <c r="B257" s="9">
-        <v>98.558999999999997</v>
+        <v>98.436999999999998</v>
       </c>
       <c r="C257" s="9">
-        <v>98.558999999999997</v>
+        <v>98.436999999999998</v>
       </c>
       <c r="D257" s="4"/>
     </row>
@@ -11577,11 +11577,11 @@
       <c r="A258" t="s">
         <v>26</v>
       </c>
-      <c r="B258" s="10">
-        <v>98.559100000000001</v>
-      </c>
-      <c r="C258" s="10">
-        <v>98.568899999999999</v>
+      <c r="B258" s="9">
+        <v>98.437100000000001</v>
+      </c>
+      <c r="C258" s="9">
+        <v>98.445899999999995</v>
       </c>
       <c r="D258" s="4"/>
     </row>
@@ -11590,10 +11590,10 @@
         <v>27</v>
       </c>
       <c r="B259" s="9">
-        <v>98.569000000000003</v>
+        <v>98.446000000000055</v>
       </c>
       <c r="C259" s="9">
-        <v>98.569000000000003</v>
+        <v>98.446000000000055</v>
       </c>
       <c r="D259" s="4"/>
     </row>
@@ -11602,10 +11602,10 @@
         <v>26</v>
       </c>
       <c r="B260" s="10">
-        <v>98.569100000000006</v>
+        <v>98.446100000000058</v>
       </c>
       <c r="C260" s="10">
-        <v>98.57889999999999</v>
+        <v>98.447900000000004</v>
       </c>
       <c r="D260" s="4"/>
     </row>
@@ -11614,10 +11614,10 @@
         <v>27</v>
       </c>
       <c r="B261" s="9">
-        <v>98.578999999999994</v>
+        <v>98.447999999999993</v>
       </c>
       <c r="C261" s="9">
-        <v>98.578999999999994</v>
+        <v>98.447999999999993</v>
       </c>
       <c r="D261" s="4"/>
     </row>
@@ -11625,11 +11625,11 @@
       <c r="A262" t="s">
         <v>26</v>
       </c>
-      <c r="B262" s="10">
-        <v>98.579099999999997</v>
-      </c>
-      <c r="C262" s="10">
-        <v>98.587899999999991</v>
+      <c r="B262" s="9">
+        <v>98.448099999999997</v>
+      </c>
+      <c r="C262" s="9">
+        <v>98.4559</v>
       </c>
       <c r="D262" s="4"/>
     </row>
@@ -11638,10 +11638,10 @@
         <v>27</v>
       </c>
       <c r="B263" s="9">
-        <v>98.587999999999994</v>
+        <v>98.456000000000003</v>
       </c>
       <c r="C263" s="9">
-        <v>98.587999999999994</v>
+        <v>98.456000000000003</v>
       </c>
       <c r="D263" s="4"/>
     </row>
@@ -11650,10 +11650,10 @@
         <v>26</v>
       </c>
       <c r="B264" s="10">
-        <v>98.588099999999997</v>
+        <v>98.456100000000006</v>
       </c>
       <c r="C264" s="10">
-        <v>98.597899999999996</v>
+        <v>98.465899999999991</v>
       </c>
       <c r="D264" s="4"/>
     </row>
@@ -11662,10 +11662,10 @@
         <v>27</v>
       </c>
       <c r="B265" s="9">
-        <v>98.597999999999999</v>
+        <v>98.465999999999994</v>
       </c>
       <c r="C265" s="9">
-        <v>98.597999999999999</v>
+        <v>98.465999999999994</v>
       </c>
       <c r="D265" s="4"/>
     </row>
@@ -11674,10 +11674,10 @@
         <v>26</v>
       </c>
       <c r="B266" s="10">
-        <v>98.598100000000002</v>
+        <v>98.466099999999997</v>
       </c>
       <c r="C266" s="10">
-        <v>98.606899999999996</v>
+        <v>98.475899999999996</v>
       </c>
       <c r="D266" s="4"/>
     </row>
@@ -11686,10 +11686,10 @@
         <v>27</v>
       </c>
       <c r="B267" s="9">
-        <v>98.606999999999999</v>
+        <v>98.475999999999999</v>
       </c>
       <c r="C267" s="9">
-        <v>98.606999999999999</v>
+        <v>98.475999999999999</v>
       </c>
       <c r="D267" s="4"/>
     </row>
@@ -11698,10 +11698,10 @@
         <v>26</v>
       </c>
       <c r="B268" s="10">
-        <v>98.607100000000003</v>
+        <v>98.476100000000002</v>
       </c>
       <c r="C268" s="10">
-        <v>98.614899999999992</v>
+        <v>98.484899999999996</v>
       </c>
       <c r="D268" s="4"/>
     </row>
@@ -11710,10 +11710,10 @@
         <v>27</v>
       </c>
       <c r="B269" s="9">
-        <v>98.614999999999995</v>
+        <v>98.484999999999999</v>
       </c>
       <c r="C269" s="9">
-        <v>98.614999999999995</v>
+        <v>98.484999999999999</v>
       </c>
       <c r="D269" s="4"/>
     </row>
@@ -11722,10 +11722,10 @@
         <v>26</v>
       </c>
       <c r="B270" s="10">
-        <v>98.615099999999998</v>
+        <v>98.485100000000003</v>
       </c>
       <c r="C270" s="10">
-        <v>98.623899999999992</v>
+        <v>98.486899999999991</v>
       </c>
       <c r="D270" s="4"/>
     </row>
@@ -11734,10 +11734,10 @@
         <v>27</v>
       </c>
       <c r="B271" s="9">
-        <v>98.623999999999995</v>
+        <v>98.486999999999995</v>
       </c>
       <c r="C271" s="9">
-        <v>98.623999999999995</v>
+        <v>98.486999999999995</v>
       </c>
       <c r="D271" s="4"/>
     </row>
@@ -11746,10 +11746,10 @@
         <v>26</v>
       </c>
       <c r="B272" s="10">
-        <v>98.624099999999999</v>
+        <v>98.487099999999998</v>
       </c>
       <c r="C272" s="10">
-        <v>98.633899999999997</v>
+        <v>98.488900000000001</v>
       </c>
       <c r="D272" s="4"/>
     </row>
@@ -11758,10 +11758,10 @@
         <v>27</v>
       </c>
       <c r="B273" s="9">
-        <v>98.634</v>
+        <v>98.489000000000004</v>
       </c>
       <c r="C273" s="9">
-        <v>98.634</v>
+        <v>98.489000000000004</v>
       </c>
       <c r="D273" s="4"/>
     </row>
@@ -11770,10 +11770,10 @@
         <v>26</v>
       </c>
       <c r="B274" s="10">
-        <v>98.634100000000004</v>
+        <v>98.489100000000008</v>
       </c>
       <c r="C274" s="10">
-        <v>98.642899999999997</v>
+        <v>98.489900000000006</v>
       </c>
       <c r="D274" s="4"/>
     </row>
@@ -11782,10 +11782,10 @@
         <v>27</v>
       </c>
       <c r="B275" s="9">
-        <v>98.643000000000001</v>
+        <v>98.49</v>
       </c>
       <c r="C275" s="9">
-        <v>98.643000000000001</v>
+        <v>98.49</v>
       </c>
       <c r="D275" s="4"/>
     </row>
@@ -11794,10 +11794,10 @@
         <v>26</v>
       </c>
       <c r="B276" s="10">
-        <v>98.643100000000004</v>
+        <v>98.490099999999998</v>
       </c>
       <c r="C276" s="10">
-        <v>98.650899999999993</v>
+        <v>98.499899999999997</v>
       </c>
       <c r="D276" s="4"/>
     </row>
@@ -11806,10 +11806,10 @@
         <v>27</v>
       </c>
       <c r="B277" s="9">
-        <v>98.650999999999996</v>
+        <v>98.5</v>
       </c>
       <c r="C277" s="9">
-        <v>98.650999999999996</v>
+        <v>98.5</v>
       </c>
       <c r="D277" s="4"/>
     </row>
@@ -11818,10 +11818,10 @@
         <v>26</v>
       </c>
       <c r="B278" s="10">
-        <v>98.6511</v>
+        <v>98.500100000000003</v>
       </c>
       <c r="C278" s="10">
-        <v>98.660899999999998</v>
+        <v>98.509900000000002</v>
       </c>
       <c r="D278" s="4"/>
     </row>
@@ -11830,10 +11830,10 @@
         <v>27</v>
       </c>
       <c r="B279" s="9">
-        <v>98.661000000000001</v>
+        <v>98.51</v>
       </c>
       <c r="C279" s="9">
-        <v>98.661000000000001</v>
+        <v>98.51</v>
       </c>
       <c r="D279" s="4"/>
     </row>
@@ -11842,10 +11842,10 @@
         <v>26</v>
       </c>
       <c r="B280" s="10">
-        <v>98.661100000000005</v>
+        <v>98.510100000000008</v>
       </c>
       <c r="C280" s="10">
-        <v>98.670900000000003</v>
+        <v>98.519900000000007</v>
       </c>
       <c r="D280" s="4"/>
     </row>
@@ -11854,10 +11854,10 @@
         <v>27</v>
       </c>
       <c r="B281" s="9">
-        <v>98.671000000000006</v>
+        <v>98.52000000000001</v>
       </c>
       <c r="C281" s="9">
-        <v>98.671000000000006</v>
+        <v>98.52000000000001</v>
       </c>
       <c r="D281" s="4"/>
     </row>
@@ -11866,10 +11866,10 @@
         <v>26</v>
       </c>
       <c r="B282" s="10">
-        <v>98.67110000000001</v>
+        <v>98.520100000000014</v>
       </c>
       <c r="C282" s="10">
-        <v>98.678899999999999</v>
+        <v>98.529900000000012</v>
       </c>
       <c r="D282" s="4"/>
     </row>
@@ -11878,10 +11878,10 @@
         <v>27</v>
       </c>
       <c r="B283" s="9">
-        <v>98.679000000000002</v>
+        <v>98.530000000000015</v>
       </c>
       <c r="C283" s="9">
-        <v>98.679000000000002</v>
+        <v>98.530000000000015</v>
       </c>
       <c r="D283" s="4"/>
     </row>
@@ -11890,10 +11890,10 @@
         <v>26</v>
       </c>
       <c r="B284" s="10">
-        <v>98.679100000000005</v>
+        <v>98.530100000000019</v>
       </c>
       <c r="C284" s="10">
-        <v>98.68889999999999</v>
+        <v>98.538899999999998</v>
       </c>
       <c r="D284" s="4"/>
     </row>
@@ -11902,10 +11902,10 @@
         <v>27</v>
       </c>
       <c r="B285" s="9">
-        <v>98.688999999999993</v>
+        <v>98.539000000000001</v>
       </c>
       <c r="C285" s="9">
-        <v>98.688999999999993</v>
+        <v>98.539000000000001</v>
       </c>
       <c r="D285" s="4"/>
     </row>
@@ -11914,10 +11914,10 @@
         <v>26</v>
       </c>
       <c r="B286" s="10">
-        <v>98.689099999999996</v>
+        <v>98.539100000000005</v>
       </c>
       <c r="C286" s="10">
-        <v>98.698899999999995</v>
+        <v>98.548900000000003</v>
       </c>
       <c r="D286" s="4"/>
     </row>
@@ -11926,10 +11926,10 @@
         <v>27</v>
       </c>
       <c r="B287" s="9">
-        <v>98.698999999999998</v>
+        <v>98.549000000000007</v>
       </c>
       <c r="C287" s="9">
-        <v>98.698999999999998</v>
+        <v>98.549000000000007</v>
       </c>
       <c r="D287" s="4"/>
     </row>
@@ -11938,10 +11938,10 @@
         <v>26</v>
       </c>
       <c r="B288" s="10">
-        <v>98.699100000000001</v>
+        <v>98.54910000000001</v>
       </c>
       <c r="C288" s="10">
-        <v>98.7089</v>
+        <v>98.558899999999994</v>
       </c>
       <c r="D288" s="4"/>
     </row>
@@ -11950,10 +11950,10 @@
         <v>27</v>
       </c>
       <c r="B289" s="9">
-        <v>98.709000000000003</v>
+        <v>98.558999999999997</v>
       </c>
       <c r="C289" s="9">
-        <v>98.709000000000003</v>
+        <v>98.558999999999997</v>
       </c>
       <c r="D289" s="4"/>
     </row>
@@ -11962,10 +11962,10 @@
         <v>26</v>
       </c>
       <c r="B290" s="10">
-        <v>98.709100000000007</v>
+        <v>98.559100000000001</v>
       </c>
       <c r="C290" s="10">
-        <v>98.718899999999991</v>
+        <v>98.568899999999999</v>
       </c>
       <c r="D290" s="4"/>
     </row>
@@ -11974,10 +11974,10 @@
         <v>27</v>
       </c>
       <c r="B291" s="9">
-        <v>98.718999999999994</v>
+        <v>98.569000000000003</v>
       </c>
       <c r="C291" s="9">
-        <v>98.718999999999994</v>
+        <v>98.569000000000003</v>
       </c>
       <c r="D291" s="4"/>
     </row>
@@ -11986,10 +11986,10 @@
         <v>26</v>
       </c>
       <c r="B292" s="10">
-        <v>98.719099999999997</v>
+        <v>98.569100000000006</v>
       </c>
       <c r="C292" s="10">
-        <v>98.726900000000001</v>
+        <v>98.57889999999999</v>
       </c>
       <c r="D292" s="4"/>
     </row>
@@ -11998,10 +11998,10 @@
         <v>27</v>
       </c>
       <c r="B293" s="9">
-        <v>98.727000000000004</v>
+        <v>98.578999999999994</v>
       </c>
       <c r="C293" s="9">
-        <v>98.727000000000004</v>
+        <v>98.578999999999994</v>
       </c>
       <c r="D293" s="4"/>
     </row>
@@ -12010,10 +12010,10 @@
         <v>26</v>
       </c>
       <c r="B294" s="10">
-        <v>98.727100000000007</v>
+        <v>98.579099999999997</v>
       </c>
       <c r="C294" s="10">
-        <v>98.736899999999991</v>
+        <v>98.587899999999991</v>
       </c>
       <c r="D294" s="4"/>
     </row>
@@ -12022,10 +12022,10 @@
         <v>27</v>
       </c>
       <c r="B295" s="9">
-        <v>98.736999999999995</v>
+        <v>98.587999999999994</v>
       </c>
       <c r="C295" s="9">
-        <v>98.736999999999995</v>
+        <v>98.587999999999994</v>
       </c>
       <c r="D295" s="4"/>
     </row>
@@ -12034,10 +12034,10 @@
         <v>26</v>
       </c>
       <c r="B296" s="10">
-        <v>98.737099999999998</v>
+        <v>98.588099999999997</v>
       </c>
       <c r="C296" s="10">
-        <v>98.745899999999992</v>
+        <v>98.597899999999996</v>
       </c>
       <c r="D296" s="4"/>
     </row>
@@ -12046,10 +12046,10 @@
         <v>27</v>
       </c>
       <c r="B297" s="9">
-        <v>98.745999999999995</v>
+        <v>98.597999999999999</v>
       </c>
       <c r="C297" s="9">
-        <v>98.745999999999995</v>
+        <v>98.597999999999999</v>
       </c>
       <c r="D297" s="4"/>
     </row>
@@ -12058,10 +12058,10 @@
         <v>26</v>
       </c>
       <c r="B298" s="10">
-        <v>98.746099999999998</v>
+        <v>98.598100000000002</v>
       </c>
       <c r="C298" s="10">
-        <v>98.756900000000002</v>
+        <v>98.606899999999996</v>
       </c>
       <c r="D298" s="4"/>
     </row>
@@ -12070,10 +12070,10 @@
         <v>27</v>
       </c>
       <c r="B299" s="9">
-        <v>98.757000000000005</v>
+        <v>98.606999999999999</v>
       </c>
       <c r="C299" s="9">
-        <v>98.757000000000005</v>
+        <v>98.606999999999999</v>
       </c>
       <c r="D299" s="4"/>
     </row>
@@ -12082,10 +12082,10 @@
         <v>26</v>
       </c>
       <c r="B300" s="10">
-        <v>98.757100000000008</v>
+        <v>98.607100000000003</v>
       </c>
       <c r="C300" s="10">
-        <v>98.762900000000002</v>
+        <v>98.614899999999992</v>
       </c>
       <c r="D300" s="4"/>
     </row>
@@ -12094,10 +12094,10 @@
         <v>27</v>
       </c>
       <c r="B301" s="9">
-        <v>98.763000000000005</v>
+        <v>98.614999999999995</v>
       </c>
       <c r="C301" s="9">
-        <v>98.763000000000005</v>
+        <v>98.614999999999995</v>
       </c>
       <c r="D301" s="4"/>
     </row>
@@ -12106,10 +12106,10 @@
         <v>26</v>
       </c>
       <c r="B302" s="10">
-        <v>98.763100000000009</v>
+        <v>98.615099999999998</v>
       </c>
       <c r="C302" s="10">
-        <v>98.764899999999997</v>
+        <v>98.623899999999992</v>
       </c>
       <c r="D302" s="4"/>
     </row>
@@ -12118,10 +12118,10 @@
         <v>27</v>
       </c>
       <c r="B303" s="9">
-        <v>98.765000000000001</v>
+        <v>98.623999999999995</v>
       </c>
       <c r="C303" s="9">
-        <v>98.765000000000001</v>
+        <v>98.623999999999995</v>
       </c>
       <c r="D303" s="4"/>
     </row>
@@ -12130,10 +12130,10 @@
         <v>26</v>
       </c>
       <c r="B304" s="10">
-        <v>98.765100000000004</v>
+        <v>98.624099999999999</v>
       </c>
       <c r="C304" s="10">
-        <v>98.329899999999995</v>
+        <v>98.633899999999997</v>
       </c>
       <c r="D304" s="4"/>
     </row>
@@ -12142,10 +12142,10 @@
         <v>27</v>
       </c>
       <c r="B305" s="9">
-        <v>98.33</v>
+        <v>98.634</v>
       </c>
       <c r="C305" s="9">
-        <v>98.33</v>
+        <v>98.634</v>
       </c>
       <c r="D305" s="4"/>
     </row>
@@ -12154,10 +12154,10 @@
         <v>26</v>
       </c>
       <c r="B306" s="10">
-        <v>98.330100000000002</v>
+        <v>98.634100000000004</v>
       </c>
       <c r="C306" s="10">
-        <v>98.3309</v>
+        <v>98.642899999999997</v>
       </c>
       <c r="D306" s="4"/>
     </row>
@@ -12166,10 +12166,10 @@
         <v>27</v>
       </c>
       <c r="B307" s="9">
-        <v>98.331000000000003</v>
+        <v>98.643000000000001</v>
       </c>
       <c r="C307" s="9">
-        <v>98.331000000000003</v>
+        <v>98.643000000000001</v>
       </c>
       <c r="D307" s="4"/>
     </row>
@@ -12178,10 +12178,10 @@
         <v>26</v>
       </c>
       <c r="B308" s="10">
-        <v>98.331100000000006</v>
+        <v>98.643100000000004</v>
       </c>
       <c r="C308" s="10">
-        <v>98.341899999999995</v>
+        <v>98.650899999999993</v>
       </c>
       <c r="D308" s="4"/>
     </row>
@@ -12190,10 +12190,10 @@
         <v>27</v>
       </c>
       <c r="B309" s="9">
-        <v>98.341999999999999</v>
+        <v>98.650999999999996</v>
       </c>
       <c r="C309" s="9">
-        <v>98.341999999999999</v>
+        <v>98.650999999999996</v>
       </c>
       <c r="D309" s="4"/>
     </row>
@@ -12202,10 +12202,10 @@
         <v>26</v>
       </c>
       <c r="B310" s="10">
-        <v>98.342100000000002</v>
+        <v>98.6511</v>
       </c>
       <c r="C310" s="10">
-        <v>98.3489</v>
+        <v>98.660899999999998</v>
       </c>
       <c r="D310" s="4"/>
     </row>
@@ -12214,10 +12214,10 @@
         <v>27</v>
       </c>
       <c r="B311" s="9">
-        <v>98.349000000000004</v>
+        <v>98.661000000000001</v>
       </c>
       <c r="C311" s="9">
-        <v>98.349000000000004</v>
+        <v>98.661000000000001</v>
       </c>
       <c r="D311" s="4"/>
     </row>
@@ -12226,10 +12226,10 @@
         <v>26</v>
       </c>
       <c r="B312" s="10">
-        <v>98.349100000000007</v>
+        <v>98.661100000000005</v>
       </c>
       <c r="C312" s="10">
-        <v>98.308899999999994</v>
+        <v>98.670900000000003</v>
       </c>
       <c r="D312" s="4"/>
     </row>
@@ -12238,10 +12238,10 @@
         <v>27</v>
       </c>
       <c r="B313" s="9">
-        <v>98.308999999999997</v>
+        <v>98.671000000000006</v>
       </c>
       <c r="C313" s="9">
-        <v>98.308999999999997</v>
+        <v>98.671000000000006</v>
       </c>
       <c r="D313" s="4"/>
     </row>
@@ -12250,10 +12250,10 @@
         <v>26</v>
       </c>
       <c r="B314" s="10">
-        <v>98.309100000000001</v>
+        <v>98.67110000000001</v>
       </c>
       <c r="C314" s="10">
-        <v>98.367899999999992</v>
+        <v>98.678899999999999</v>
       </c>
       <c r="D314" s="4"/>
     </row>
@@ -12262,10 +12262,10 @@
         <v>27</v>
       </c>
       <c r="B315" s="9">
-        <v>98.367999999999995</v>
+        <v>98.679000000000002</v>
       </c>
       <c r="C315" s="9">
-        <v>98.367999999999995</v>
+        <v>98.679000000000002</v>
       </c>
       <c r="D315" s="4"/>
     </row>
@@ -12274,10 +12274,10 @@
         <v>26</v>
       </c>
       <c r="B316" s="10">
-        <v>98.368099999999998</v>
+        <v>98.679100000000005</v>
       </c>
       <c r="C316" s="10">
-        <v>98.370899999999992</v>
+        <v>98.68889999999999</v>
       </c>
       <c r="D316" s="4"/>
     </row>
@@ -12286,10 +12286,10 @@
         <v>27</v>
       </c>
       <c r="B317" s="9">
-        <v>98.370999999999995</v>
+        <v>98.688999999999993</v>
       </c>
       <c r="C317" s="9">
-        <v>98.370999999999995</v>
+        <v>98.688999999999993</v>
       </c>
       <c r="D317" s="4"/>
     </row>
@@ -12298,10 +12298,10 @@
         <v>26</v>
       </c>
       <c r="B318" s="10">
-        <v>98.371099999999998</v>
+        <v>98.689099999999996</v>
       </c>
       <c r="C318" s="10">
-        <v>98.374899999999997</v>
+        <v>98.698899999999995</v>
       </c>
       <c r="D318" s="4"/>
     </row>
@@ -12310,10 +12310,10 @@
         <v>27</v>
       </c>
       <c r="B319" s="9">
-        <v>98.375</v>
+        <v>98.698999999999998</v>
       </c>
       <c r="C319" s="9">
-        <v>98.375</v>
+        <v>98.698999999999998</v>
       </c>
       <c r="D319" s="4"/>
     </row>
@@ -12322,10 +12322,10 @@
         <v>26</v>
       </c>
       <c r="B320" s="10">
-        <v>98.375100000000003</v>
+        <v>98.699100000000001</v>
       </c>
       <c r="C320" s="10">
-        <v>98.377899999999997</v>
+        <v>98.7089</v>
       </c>
       <c r="D320" s="4"/>
     </row>
@@ -12334,10 +12334,10 @@
         <v>27</v>
       </c>
       <c r="B321" s="9">
-        <v>98.378</v>
+        <v>98.709000000000003</v>
       </c>
       <c r="C321" s="9">
-        <v>98.378</v>
+        <v>98.709000000000003</v>
       </c>
       <c r="D321" s="4"/>
     </row>
@@ -12346,10 +12346,10 @@
         <v>26</v>
       </c>
       <c r="B322" s="10">
-        <v>98.378100000000003</v>
+        <v>98.709100000000007</v>
       </c>
       <c r="C322" s="10">
-        <v>98.381900000000002</v>
+        <v>98.718899999999991</v>
       </c>
       <c r="D322" s="4"/>
     </row>
@@ -12358,10 +12358,10 @@
         <v>27</v>
       </c>
       <c r="B323" s="9">
-        <v>98.382000000000005</v>
+        <v>98.718999999999994</v>
       </c>
       <c r="C323" s="9">
-        <v>98.382000000000005</v>
+        <v>98.718999999999994</v>
       </c>
       <c r="D323" s="4"/>
     </row>
@@ -12370,10 +12370,10 @@
         <v>26</v>
       </c>
       <c r="B324" s="10">
-        <v>98.382100000000008</v>
+        <v>98.719099999999997</v>
       </c>
       <c r="C324" s="10">
-        <v>98.387900000000002</v>
+        <v>98.726900000000001</v>
       </c>
       <c r="D324" s="4"/>
     </row>
@@ -12382,10 +12382,10 @@
         <v>27</v>
       </c>
       <c r="B325" s="9">
-        <v>98.388000000000005</v>
+        <v>98.727000000000004</v>
       </c>
       <c r="C325" s="9">
-        <v>98.388000000000005</v>
+        <v>98.727000000000004</v>
       </c>
       <c r="D325" s="4"/>
     </row>
@@ -12394,10 +12394,10 @@
         <v>26</v>
       </c>
       <c r="B326" s="10">
-        <v>98.388100000000009</v>
+        <v>98.727100000000007</v>
       </c>
       <c r="C326" s="10">
-        <v>98.389899999999997</v>
+        <v>98.736899999999991</v>
       </c>
       <c r="D326" s="4"/>
     </row>
@@ -12406,10 +12406,10 @@
         <v>27</v>
       </c>
       <c r="B327" s="9">
-        <v>98.39</v>
+        <v>98.736999999999995</v>
       </c>
       <c r="C327" s="9">
-        <v>98.39</v>
+        <v>98.736999999999995</v>
       </c>
       <c r="D327" s="4"/>
     </row>
@@ -12418,10 +12418,10 @@
         <v>26</v>
       </c>
       <c r="B328" s="10">
-        <v>98.390100000000004</v>
+        <v>98.737099999999998</v>
       </c>
       <c r="C328" s="10">
-        <v>98.395899999999997</v>
+        <v>98.745899999999992</v>
       </c>
       <c r="D328" s="4"/>
     </row>
@@ -12430,10 +12430,10 @@
         <v>27</v>
       </c>
       <c r="B329" s="9">
-        <v>98.396000000000001</v>
+        <v>98.745999999999995</v>
       </c>
       <c r="C329" s="9">
-        <v>98.396000000000001</v>
+        <v>98.745999999999995</v>
       </c>
       <c r="D329" s="4"/>
     </row>
@@ -12442,10 +12442,10 @@
         <v>26</v>
       </c>
       <c r="B330" s="10">
-        <v>98.396100000000004</v>
+        <v>98.746099999999998</v>
       </c>
       <c r="C330" s="10">
-        <v>98.399900000000002</v>
+        <v>98.756900000000002</v>
       </c>
       <c r="D330" s="4"/>
     </row>
@@ -12454,10 +12454,10 @@
         <v>27</v>
       </c>
       <c r="B331" s="9">
-        <v>98.4</v>
+        <v>98.757000000000005</v>
       </c>
       <c r="C331" s="9">
-        <v>98.4</v>
+        <v>98.757000000000005</v>
       </c>
       <c r="D331" s="4"/>
     </row>
@@ -12466,10 +12466,10 @@
         <v>26</v>
       </c>
       <c r="B332" s="10">
-        <v>98.400100000000009</v>
+        <v>98.757100000000008</v>
       </c>
       <c r="C332" s="10">
-        <v>98.402900000000002</v>
+        <v>98.762900000000002</v>
       </c>
       <c r="D332" s="4"/>
     </row>
@@ -12478,10 +12478,10 @@
         <v>27</v>
       </c>
       <c r="B333" s="9">
-        <v>98.403000000000006</v>
+        <v>98.763000000000005</v>
       </c>
       <c r="C333" s="9">
-        <v>98.403000000000006</v>
+        <v>98.763000000000005</v>
       </c>
       <c r="D333" s="4"/>
     </row>
@@ -12490,10 +12490,10 @@
         <v>26</v>
       </c>
       <c r="B334" s="10">
-        <v>98.403100000000009</v>
+        <v>98.763100000000009</v>
       </c>
       <c r="C334" s="10">
-        <v>98.406899999999993</v>
+        <v>98.763900000000007</v>
       </c>
       <c r="D334" s="4"/>
     </row>
@@ -12502,10 +12502,10 @@
         <v>27</v>
       </c>
       <c r="B335" s="9">
-        <v>98.406999999999996</v>
+        <v>98.763999999999996</v>
       </c>
       <c r="C335" s="9">
-        <v>98.406999999999996</v>
+        <v>98.763999999999996</v>
       </c>
       <c r="D335" s="4"/>
     </row>
@@ -12514,10 +12514,10 @@
         <v>26</v>
       </c>
       <c r="B336" s="10">
-        <v>98.4071</v>
-      </c>
-      <c r="C336" s="10">
-        <v>98.410899999999998</v>
+        <v>98.764099999999999</v>
+      </c>
+      <c r="C336" s="9">
+        <v>98.764899999999997</v>
       </c>
       <c r="D336" s="4"/>
     </row>
@@ -12526,10 +12526,10 @@
         <v>27</v>
       </c>
       <c r="B337" s="9">
-        <v>98.411000000000001</v>
+        <v>98.765000000000001</v>
       </c>
       <c r="C337" s="9">
-        <v>98.411000000000001</v>
+        <v>98.765000000000001</v>
       </c>
       <c r="D337" s="4"/>
     </row>
@@ -12538,22 +12538,22 @@
         <v>26</v>
       </c>
       <c r="B338" s="10">
-        <v>98.411100000000005</v>
+        <v>98.765100000000004</v>
       </c>
       <c r="C338" s="10">
-        <v>98.418899999999994</v>
+        <v>98.765900000000002</v>
       </c>
       <c r="D338" s="4"/>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>27</v>
       </c>
       <c r="B339" s="9">
-        <v>98.418999999999997</v>
+        <v>98.766000000000005</v>
       </c>
       <c r="C339" s="9">
-        <v>98.418999999999997</v>
+        <v>98.766000000000005</v>
       </c>
       <c r="D339" s="4"/>
     </row>
@@ -12562,10 +12562,10 @@
         <v>26</v>
       </c>
       <c r="B340" s="10">
-        <v>98.4191</v>
+        <v>98.766100000000009</v>
       </c>
       <c r="C340" s="10">
-        <v>98.428899999999999</v>
+        <v>98.772899999999993</v>
       </c>
       <c r="D340" s="4"/>
     </row>
@@ -12574,10 +12574,10 @@
         <v>27</v>
       </c>
       <c r="B341" s="9">
-        <v>98.429000000000002</v>
+        <v>98.772999999999996</v>
       </c>
       <c r="C341" s="9">
-        <v>98.429000000000002</v>
+        <v>98.772999999999996</v>
       </c>
       <c r="D341" s="4"/>
     </row>
@@ -12586,10 +12586,10 @@
         <v>26</v>
       </c>
       <c r="B342" s="10">
-        <v>98.429100000000005</v>
+        <v>98.773099999999999</v>
       </c>
       <c r="C342" s="10">
-        <v>98.436899999999994</v>
+        <v>98.782899999999998</v>
       </c>
       <c r="D342" s="4"/>
     </row>
@@ -12598,10 +12598,10 @@
         <v>27</v>
       </c>
       <c r="B343" s="9">
-        <v>98.436999999999998</v>
+        <v>98.783000000000001</v>
       </c>
       <c r="C343" s="9">
-        <v>98.436999999999998</v>
+        <v>98.783000000000001</v>
       </c>
       <c r="D343" s="4"/>
     </row>
@@ -12610,10 +12610,10 @@
         <v>26</v>
       </c>
       <c r="B344" s="10">
-        <v>98.437100000000001</v>
+        <v>98.783100000000005</v>
       </c>
       <c r="C344" s="10">
-        <v>98.445899999999995</v>
+        <v>98.792900000000003</v>
       </c>
       <c r="D344" s="4"/>
     </row>
@@ -12622,10 +12622,10 @@
         <v>27</v>
       </c>
       <c r="B345" s="9">
-        <v>98.445999999999998</v>
+        <v>98.793000000000006</v>
       </c>
       <c r="C345" s="9">
-        <v>98.445999999999998</v>
+        <v>98.793000000000006</v>
       </c>
       <c r="D345" s="4"/>
     </row>
@@ -12634,10 +12634,10 @@
         <v>26</v>
       </c>
       <c r="B346" s="10">
-        <v>98.446100000000001</v>
+        <v>98.79310000000001</v>
       </c>
       <c r="C346" s="10">
-        <v>98.44789999999999</v>
+        <v>98.802900000000008</v>
       </c>
       <c r="D346" s="4"/>
     </row>
@@ -12646,10 +12646,10 @@
         <v>27</v>
       </c>
       <c r="B347" s="9">
-        <v>98.447999999999993</v>
+        <v>98.803000000000011</v>
       </c>
       <c r="C347" s="9">
-        <v>98.447999999999993</v>
+        <v>98.803000000000011</v>
       </c>
       <c r="D347" s="4"/>
     </row>
@@ -12658,10 +12658,10 @@
         <v>26</v>
       </c>
       <c r="B348" s="10">
-        <v>98.448099999999997</v>
+        <v>98.803100000000015</v>
       </c>
       <c r="C348" s="10">
-        <v>98.763899999999992</v>
+        <v>98.812900000000013</v>
       </c>
       <c r="D348" s="4"/>
     </row>
@@ -12670,10 +12670,10 @@
         <v>27</v>
       </c>
       <c r="B349" s="9">
-        <v>98.763999999999996</v>
+        <v>98.813000000000017</v>
       </c>
       <c r="C349" s="9">
-        <v>98.763999999999996</v>
+        <v>98.813000000000017</v>
       </c>
       <c r="D349" s="4"/>
     </row>
@@ -12682,10 +12682,10 @@
         <v>26</v>
       </c>
       <c r="B350" s="10">
-        <v>98.764099999999999</v>
+        <v>98.81310000000002</v>
       </c>
       <c r="C350" s="10">
-        <v>98.765900000000002</v>
+        <v>98.822900000000018</v>
       </c>
       <c r="D350" s="4"/>
     </row>
@@ -12694,10 +12694,10 @@
         <v>27</v>
       </c>
       <c r="B351" s="9">
-        <v>98.766000000000005</v>
+        <v>98.823000000000022</v>
       </c>
       <c r="C351" s="9">
-        <v>98.766000000000005</v>
+        <v>98.823000000000022</v>
       </c>
       <c r="D351" s="4"/>
     </row>
@@ -12706,10 +12706,10 @@
         <v>26</v>
       </c>
       <c r="B352" s="10">
-        <v>98.766100000000009</v>
+        <v>98.823100000000025</v>
       </c>
       <c r="C352" s="10">
-        <v>98.772899999999993</v>
+        <v>98.832900000000024</v>
       </c>
       <c r="D352" s="4"/>
     </row>
@@ -12718,10 +12718,10 @@
         <v>27</v>
       </c>
       <c r="B353" s="9">
-        <v>98.772999999999996</v>
+        <v>98.833000000000027</v>
       </c>
       <c r="C353" s="9">
-        <v>98.772999999999996</v>
+        <v>98.833000000000027</v>
       </c>
       <c r="D353" s="4"/>
     </row>
@@ -12730,10 +12730,10 @@
         <v>26</v>
       </c>
       <c r="B354" s="10">
-        <v>98.773099999999999</v>
+        <v>98.83310000000003</v>
       </c>
       <c r="C354" s="10">
-        <v>98.782899999999998</v>
+        <v>98.842900000000029</v>
       </c>
       <c r="D354" s="4"/>
     </row>
@@ -12742,10 +12742,10 @@
         <v>27</v>
       </c>
       <c r="B355" s="9">
-        <v>98.783000000000001</v>
+        <v>98.843000000000032</v>
       </c>
       <c r="C355" s="9">
-        <v>98.783000000000001</v>
+        <v>98.843000000000032</v>
       </c>
       <c r="D355" s="4"/>
     </row>
@@ -12754,10 +12754,10 @@
         <v>26</v>
       </c>
       <c r="B356" s="10">
-        <v>98.783100000000005</v>
+        <v>98.843100000000035</v>
       </c>
       <c r="C356" s="10">
-        <v>98.792900000000003</v>
+        <v>98.852900000000034</v>
       </c>
       <c r="D356" s="4"/>
     </row>
@@ -12766,10 +12766,10 @@
         <v>27</v>
       </c>
       <c r="B357" s="9">
-        <v>98.793000000000006</v>
+        <v>98.853000000000037</v>
       </c>
       <c r="C357" s="9">
-        <v>98.793000000000006</v>
+        <v>98.853000000000037</v>
       </c>
       <c r="D357" s="4"/>
     </row>
@@ -12778,10 +12778,10 @@
         <v>26</v>
       </c>
       <c r="B358" s="10">
-        <v>98.79310000000001</v>
+        <v>98.85310000000004</v>
       </c>
       <c r="C358" s="10">
-        <v>98.802900000000008</v>
+        <v>98.862900000000039</v>
       </c>
       <c r="D358" s="4"/>
     </row>
@@ -12790,10 +12790,10 @@
         <v>27</v>
       </c>
       <c r="B359" s="9">
-        <v>98.803000000000011</v>
+        <v>98.863000000000042</v>
       </c>
       <c r="C359" s="9">
-        <v>98.803000000000011</v>
+        <v>98.863000000000042</v>
       </c>
       <c r="D359" s="4"/>
     </row>
@@ -12802,10 +12802,10 @@
         <v>26</v>
       </c>
       <c r="B360" s="10">
-        <v>98.803100000000015</v>
+        <v>98.863100000000045</v>
       </c>
       <c r="C360" s="10">
-        <v>98.812900000000013</v>
+        <v>98.872900000000001</v>
       </c>
       <c r="D360" s="4"/>
     </row>
@@ -12814,10 +12814,10 @@
         <v>27</v>
       </c>
       <c r="B361" s="9">
-        <v>98.813000000000017</v>
+        <v>98.873000000000005</v>
       </c>
       <c r="C361" s="9">
-        <v>98.813000000000017</v>
+        <v>98.873000000000005</v>
       </c>
       <c r="D361" s="4"/>
     </row>
@@ -12826,10 +12826,10 @@
         <v>26</v>
       </c>
       <c r="B362" s="10">
-        <v>98.81310000000002</v>
+        <v>98.873100000000008</v>
       </c>
       <c r="C362" s="10">
-        <v>98.822900000000018</v>
+        <v>98.882900000000006</v>
       </c>
       <c r="D362" s="4"/>
     </row>
@@ -12838,10 +12838,10 @@
         <v>27</v>
       </c>
       <c r="B363" s="9">
-        <v>98.823000000000022</v>
+        <v>98.88300000000001</v>
       </c>
       <c r="C363" s="9">
-        <v>98.823000000000022</v>
+        <v>98.88300000000001</v>
       </c>
       <c r="D363" s="4"/>
     </row>
@@ -12850,10 +12850,10 @@
         <v>26</v>
       </c>
       <c r="B364" s="10">
-        <v>98.823100000000025</v>
+        <v>98.883100000000013</v>
       </c>
       <c r="C364" s="10">
-        <v>98.832900000000024</v>
+        <v>98.892900000000012</v>
       </c>
       <c r="D364" s="4"/>
     </row>
@@ -12862,10 +12862,10 @@
         <v>27</v>
       </c>
       <c r="B365" s="9">
-        <v>98.833000000000027</v>
+        <v>98.893000000000015</v>
       </c>
       <c r="C365" s="9">
-        <v>98.833000000000027</v>
+        <v>98.893000000000015</v>
       </c>
       <c r="D365" s="4"/>
     </row>
@@ -12874,10 +12874,10 @@
         <v>26</v>
       </c>
       <c r="B366" s="10">
-        <v>98.83310000000003</v>
+        <v>98.893100000000018</v>
       </c>
       <c r="C366" s="10">
-        <v>98.842900000000029</v>
+        <v>98.902900000000017</v>
       </c>
       <c r="D366" s="4"/>
     </row>
@@ -12886,10 +12886,10 @@
         <v>27</v>
       </c>
       <c r="B367" s="9">
-        <v>98.843000000000032</v>
+        <v>98.90300000000002</v>
       </c>
       <c r="C367" s="9">
-        <v>98.843000000000032</v>
+        <v>98.90300000000002</v>
       </c>
       <c r="D367" s="4"/>
     </row>
@@ -12898,10 +12898,10 @@
         <v>26</v>
       </c>
       <c r="B368" s="10">
-        <v>98.843100000000035</v>
+        <v>98.903100000000023</v>
       </c>
       <c r="C368" s="10">
-        <v>98.852900000000034</v>
+        <v>98.912900000000022</v>
       </c>
       <c r="D368" s="4"/>
     </row>
@@ -12910,10 +12910,10 @@
         <v>27</v>
       </c>
       <c r="B369" s="9">
-        <v>98.853000000000037</v>
+        <v>98.913000000000025</v>
       </c>
       <c r="C369" s="9">
-        <v>98.853000000000037</v>
+        <v>98.913000000000025</v>
       </c>
       <c r="D369" s="4"/>
     </row>
@@ -12922,10 +12922,10 @@
         <v>26</v>
       </c>
       <c r="B370" s="10">
-        <v>98.85310000000004</v>
+        <v>98.913100000000028</v>
       </c>
       <c r="C370" s="10">
-        <v>98.862900000000039</v>
+        <v>98.922900000000027</v>
       </c>
       <c r="D370" s="4"/>
     </row>
@@ -12934,10 +12934,10 @@
         <v>27</v>
       </c>
       <c r="B371" s="9">
-        <v>98.863000000000042</v>
+        <v>98.92300000000003</v>
       </c>
       <c r="C371" s="9">
-        <v>98.863000000000042</v>
+        <v>98.92300000000003</v>
       </c>
       <c r="D371" s="4"/>
     </row>
@@ -12946,10 +12946,10 @@
         <v>26</v>
       </c>
       <c r="B372" s="10">
-        <v>98.863100000000045</v>
+        <v>98.923100000000034</v>
       </c>
       <c r="C372" s="10">
-        <v>98.872900000000001</v>
+        <v>98.932900000000032</v>
       </c>
       <c r="D372" s="4"/>
     </row>
@@ -12958,10 +12958,10 @@
         <v>27</v>
       </c>
       <c r="B373" s="9">
-        <v>98.873000000000005</v>
+        <v>98.933000000000035</v>
       </c>
       <c r="C373" s="9">
-        <v>98.873000000000005</v>
+        <v>98.933000000000035</v>
       </c>
       <c r="D373" s="4"/>
     </row>
@@ -12970,10 +12970,10 @@
         <v>26</v>
       </c>
       <c r="B374" s="10">
-        <v>98.873100000000008</v>
+        <v>98.933100000000039</v>
       </c>
       <c r="C374" s="10">
-        <v>98.882900000000006</v>
+        <v>98.942900000000037</v>
       </c>
       <c r="D374" s="4"/>
     </row>
@@ -12982,10 +12982,10 @@
         <v>27</v>
       </c>
       <c r="B375" s="9">
-        <v>98.88300000000001</v>
+        <v>98.94300000000004</v>
       </c>
       <c r="C375" s="9">
-        <v>98.88300000000001</v>
+        <v>98.94300000000004</v>
       </c>
       <c r="D375" s="4"/>
     </row>
@@ -12994,10 +12994,10 @@
         <v>26</v>
       </c>
       <c r="B376" s="10">
-        <v>98.883100000000013</v>
+        <v>98.943100000000044</v>
       </c>
       <c r="C376" s="10">
-        <v>98.892900000000012</v>
+        <v>98.952900000000042</v>
       </c>
       <c r="D376" s="4"/>
     </row>
@@ -13006,10 +13006,10 @@
         <v>27</v>
       </c>
       <c r="B377" s="9">
-        <v>98.893000000000015</v>
+        <v>98.953000000000046</v>
       </c>
       <c r="C377" s="9">
-        <v>98.893000000000015</v>
+        <v>98.953000000000046</v>
       </c>
       <c r="D377" s="4"/>
     </row>
@@ -13018,10 +13018,10 @@
         <v>26</v>
       </c>
       <c r="B378" s="10">
-        <v>98.893100000000018</v>
+        <v>98.953100000000049</v>
       </c>
       <c r="C378" s="10">
-        <v>98.902900000000017</v>
+        <v>98.962900000000047</v>
       </c>
       <c r="D378" s="4"/>
     </row>
@@ -13030,10 +13030,10 @@
         <v>27</v>
       </c>
       <c r="B379" s="9">
-        <v>98.90300000000002</v>
+        <v>98.963000000000051</v>
       </c>
       <c r="C379" s="9">
-        <v>98.90300000000002</v>
+        <v>98.963000000000051</v>
       </c>
       <c r="D379" s="4"/>
     </row>
@@ -13042,10 +13042,10 @@
         <v>26</v>
       </c>
       <c r="B380" s="10">
-        <v>98.903100000000023</v>
+        <v>98.963100000000054</v>
       </c>
       <c r="C380" s="10">
-        <v>98.912900000000022</v>
+        <v>98.972899999999996</v>
       </c>
       <c r="D380" s="4"/>
     </row>
@@ -13054,10 +13054,10 @@
         <v>27</v>
       </c>
       <c r="B381" s="9">
-        <v>98.913000000000025</v>
+        <v>98.972999999999999</v>
       </c>
       <c r="C381" s="9">
-        <v>98.913000000000025</v>
+        <v>98.972999999999999</v>
       </c>
       <c r="D381" s="4"/>
     </row>
@@ -13066,10 +13066,10 @@
         <v>26</v>
       </c>
       <c r="B382" s="10">
-        <v>98.913100000000028</v>
+        <v>98.973100000000002</v>
       </c>
       <c r="C382" s="10">
-        <v>98.922900000000027</v>
+        <v>98.982900000000001</v>
       </c>
       <c r="D382" s="4"/>
     </row>
@@ -13078,10 +13078,10 @@
         <v>27</v>
       </c>
       <c r="B383" s="9">
-        <v>98.92300000000003</v>
+        <v>98.983000000000004</v>
       </c>
       <c r="C383" s="9">
-        <v>98.92300000000003</v>
+        <v>98.983000000000004</v>
       </c>
       <c r="D383" s="4"/>
     </row>
@@ -13090,10 +13090,10 @@
         <v>26</v>
       </c>
       <c r="B384" s="10">
-        <v>98.923100000000034</v>
+        <v>98.983100000000007</v>
       </c>
       <c r="C384" s="10">
-        <v>98.932900000000032</v>
+        <v>98.992900000000006</v>
       </c>
       <c r="D384" s="4"/>
     </row>
@@ -13102,10 +13102,10 @@
         <v>27</v>
       </c>
       <c r="B385" s="9">
-        <v>98.933000000000035</v>
+        <v>98.993000000000009</v>
       </c>
       <c r="C385" s="9">
-        <v>98.933000000000035</v>
+        <v>98.993000000000009</v>
       </c>
       <c r="D385" s="4"/>
     </row>
@@ -13114,10 +13114,10 @@
         <v>26</v>
       </c>
       <c r="B386" s="10">
-        <v>98.933100000000039</v>
+        <v>98.993100000000013</v>
       </c>
       <c r="C386" s="10">
-        <v>98.942900000000037</v>
+        <v>99.002900000000011</v>
       </c>
       <c r="D386" s="4"/>
     </row>
@@ -13126,10 +13126,10 @@
         <v>27</v>
       </c>
       <c r="B387" s="9">
-        <v>98.94300000000004</v>
+        <v>99.003000000000014</v>
       </c>
       <c r="C387" s="9">
-        <v>98.94300000000004</v>
+        <v>99.003000000000014</v>
       </c>
       <c r="D387" s="4"/>
     </row>
@@ -13138,10 +13138,10 @@
         <v>26</v>
       </c>
       <c r="B388" s="10">
-        <v>98.943100000000044</v>
+        <v>99.003100000000018</v>
       </c>
       <c r="C388" s="10">
-        <v>98.952900000000042</v>
+        <v>99.012900000000016</v>
       </c>
       <c r="D388" s="4"/>
     </row>
@@ -13150,10 +13150,10 @@
         <v>27</v>
       </c>
       <c r="B389" s="9">
-        <v>98.953000000000046</v>
+        <v>99.013000000000019</v>
       </c>
       <c r="C389" s="9">
-        <v>98.953000000000046</v>
+        <v>99.013000000000019</v>
       </c>
       <c r="D389" s="4"/>
     </row>
@@ -13162,10 +13162,10 @@
         <v>26</v>
       </c>
       <c r="B390" s="10">
-        <v>98.953100000000049</v>
+        <v>99.013100000000023</v>
       </c>
       <c r="C390" s="10">
-        <v>98.962900000000047</v>
+        <v>99.022900000000021</v>
       </c>
       <c r="D390" s="4"/>
     </row>
@@ -13174,10 +13174,10 @@
         <v>27</v>
       </c>
       <c r="B391" s="9">
-        <v>98.963000000000051</v>
+        <v>99.023000000000025</v>
       </c>
       <c r="C391" s="9">
-        <v>98.963000000000051</v>
+        <v>99.023000000000025</v>
       </c>
       <c r="D391" s="4"/>
     </row>
@@ -13186,10 +13186,10 @@
         <v>26</v>
       </c>
       <c r="B392" s="10">
-        <v>98.963100000000054</v>
+        <v>99.023100000000028</v>
       </c>
       <c r="C392" s="10">
-        <v>98.972899999999996</v>
+        <v>99.032900000000026</v>
       </c>
       <c r="D392" s="4"/>
     </row>
@@ -13198,10 +13198,10 @@
         <v>27</v>
       </c>
       <c r="B393" s="9">
-        <v>98.972999999999999</v>
+        <v>99.03300000000003</v>
       </c>
       <c r="C393" s="9">
-        <v>98.972999999999999</v>
+        <v>99.03300000000003</v>
       </c>
       <c r="D393" s="4"/>
     </row>
@@ -13210,10 +13210,10 @@
         <v>26</v>
       </c>
       <c r="B394" s="10">
-        <v>98.973100000000002</v>
+        <v>99.033100000000033</v>
       </c>
       <c r="C394" s="10">
-        <v>98.982900000000001</v>
+        <v>99.042900000000031</v>
       </c>
       <c r="D394" s="4"/>
     </row>
@@ -13222,10 +13222,10 @@
         <v>27</v>
       </c>
       <c r="B395" s="9">
-        <v>98.983000000000004</v>
+        <v>99.043000000000035</v>
       </c>
       <c r="C395" s="9">
-        <v>98.983000000000004</v>
+        <v>99.043000000000035</v>
       </c>
       <c r="D395" s="4"/>
     </row>
@@ -13234,10 +13234,10 @@
         <v>26</v>
       </c>
       <c r="B396" s="10">
-        <v>98.983100000000007</v>
+        <v>99.043100000000038</v>
       </c>
       <c r="C396" s="10">
-        <v>98.992900000000006</v>
+        <v>99.052900000000037</v>
       </c>
       <c r="D396" s="4"/>
     </row>
@@ -13246,10 +13246,10 @@
         <v>27</v>
       </c>
       <c r="B397" s="9">
-        <v>98.993000000000009</v>
+        <v>99.05300000000004</v>
       </c>
       <c r="C397" s="9">
-        <v>98.993000000000009</v>
+        <v>99.05300000000004</v>
       </c>
       <c r="D397" s="4"/>
     </row>
@@ -13258,10 +13258,10 @@
         <v>26</v>
       </c>
       <c r="B398" s="10">
-        <v>98.993100000000013</v>
+        <v>99.053100000000043</v>
       </c>
       <c r="C398" s="10">
-        <v>99.002900000000011</v>
+        <v>99.062899999999999</v>
       </c>
       <c r="D398" s="4"/>
     </row>
@@ -13270,10 +13270,10 @@
         <v>27</v>
       </c>
       <c r="B399" s="9">
-        <v>99.003000000000014</v>
+        <v>99.063000000000002</v>
       </c>
       <c r="C399" s="9">
-        <v>99.003000000000014</v>
+        <v>99.063000000000002</v>
       </c>
       <c r="D399" s="4"/>
     </row>
@@ -13282,10 +13282,10 @@
         <v>26</v>
       </c>
       <c r="B400" s="10">
-        <v>99.003100000000018</v>
+        <v>99.063100000000006</v>
       </c>
       <c r="C400" s="10">
-        <v>99.012900000000016</v>
+        <v>99.072900000000004</v>
       </c>
       <c r="D400" s="4"/>
     </row>
@@ -13294,10 +13294,10 @@
         <v>27</v>
       </c>
       <c r="B401" s="9">
-        <v>99.013000000000019</v>
+        <v>99.073000000000008</v>
       </c>
       <c r="C401" s="9">
-        <v>99.013000000000019</v>
+        <v>99.073000000000008</v>
       </c>
       <c r="D401" s="4"/>
     </row>
@@ -13306,10 +13306,10 @@
         <v>26</v>
       </c>
       <c r="B402" s="10">
-        <v>99.013100000000023</v>
+        <v>99.073100000000011</v>
       </c>
       <c r="C402" s="10">
-        <v>99.022900000000021</v>
+        <v>99.082900000000009</v>
       </c>
       <c r="D402" s="4"/>
     </row>
@@ -13318,10 +13318,10 @@
         <v>27</v>
       </c>
       <c r="B403" s="9">
-        <v>99.023000000000025</v>
+        <v>99.083000000000013</v>
       </c>
       <c r="C403" s="9">
-        <v>99.023000000000025</v>
+        <v>99.083000000000013</v>
       </c>
       <c r="D403" s="4"/>
     </row>
@@ -13330,10 +13330,10 @@
         <v>26</v>
       </c>
       <c r="B404" s="10">
-        <v>99.023100000000028</v>
+        <v>99.083100000000016</v>
       </c>
       <c r="C404" s="10">
-        <v>99.032900000000026</v>
+        <v>99.092900000000014</v>
       </c>
       <c r="D404" s="4"/>
     </row>
@@ -13342,10 +13342,10 @@
         <v>27</v>
       </c>
       <c r="B405" s="9">
-        <v>99.03300000000003</v>
+        <v>99.093000000000018</v>
       </c>
       <c r="C405" s="9">
-        <v>99.03300000000003</v>
+        <v>99.093000000000018</v>
       </c>
       <c r="D405" s="4"/>
     </row>
@@ -13354,10 +13354,10 @@
         <v>26</v>
       </c>
       <c r="B406" s="10">
-        <v>99.033100000000033</v>
+        <v>99.093100000000021</v>
       </c>
       <c r="C406" s="10">
-        <v>99.042900000000031</v>
+        <v>99.10290000000002</v>
       </c>
       <c r="D406" s="4"/>
     </row>
@@ -13366,10 +13366,10 @@
         <v>27</v>
       </c>
       <c r="B407" s="9">
-        <v>99.043000000000035</v>
+        <v>99.103000000000023</v>
       </c>
       <c r="C407" s="9">
-        <v>99.043000000000035</v>
+        <v>99.103000000000023</v>
       </c>
       <c r="D407" s="4"/>
     </row>
@@ -13378,10 +13378,10 @@
         <v>26</v>
       </c>
       <c r="B408" s="10">
-        <v>99.043100000000038</v>
+        <v>99.103100000000026</v>
       </c>
       <c r="C408" s="10">
-        <v>99.052900000000037</v>
+        <v>99.113900000000001</v>
       </c>
       <c r="D408" s="4"/>
     </row>
@@ -13390,10 +13390,10 @@
         <v>27</v>
       </c>
       <c r="B409" s="9">
-        <v>99.05300000000004</v>
+        <v>99.114000000000004</v>
       </c>
       <c r="C409" s="9">
-        <v>99.05300000000004</v>
+        <v>99.114000000000004</v>
       </c>
       <c r="D409" s="4"/>
     </row>
@@ -13402,10 +13402,10 @@
         <v>26</v>
       </c>
       <c r="B410" s="10">
-        <v>99.053100000000043</v>
+        <v>99.114100000000008</v>
       </c>
       <c r="C410" s="10">
-        <v>99.062899999999999</v>
+        <v>99.123900000000006</v>
       </c>
       <c r="D410" s="4"/>
     </row>
@@ -13414,10 +13414,10 @@
         <v>27</v>
       </c>
       <c r="B411" s="9">
-        <v>99.063000000000002</v>
+        <v>99.124000000000009</v>
       </c>
       <c r="C411" s="9">
-        <v>99.063000000000002</v>
+        <v>99.124000000000009</v>
       </c>
       <c r="D411" s="4"/>
     </row>
@@ -13426,10 +13426,10 @@
         <v>26</v>
       </c>
       <c r="B412" s="10">
-        <v>99.063100000000006</v>
+        <v>99.124100000000013</v>
       </c>
       <c r="C412" s="10">
-        <v>99.072900000000004</v>
+        <v>99.133900000000011</v>
       </c>
       <c r="D412" s="4"/>
     </row>
@@ -13438,10 +13438,10 @@
         <v>27</v>
       </c>
       <c r="B413" s="9">
-        <v>99.073000000000008</v>
+        <v>99.134000000000015</v>
       </c>
       <c r="C413" s="9">
-        <v>99.073000000000008</v>
+        <v>99.134000000000015</v>
       </c>
       <c r="D413" s="4"/>
     </row>
@@ -13450,10 +13450,10 @@
         <v>26</v>
       </c>
       <c r="B414" s="10">
-        <v>99.073100000000011</v>
+        <v>99.134100000000018</v>
       </c>
       <c r="C414" s="10">
-        <v>99.082900000000009</v>
+        <v>99.143900000000016</v>
       </c>
       <c r="D414" s="4"/>
     </row>
@@ -13462,10 +13462,10 @@
         <v>27</v>
       </c>
       <c r="B415" s="9">
-        <v>99.083000000000013</v>
+        <v>99.14400000000002</v>
       </c>
       <c r="C415" s="9">
-        <v>99.083000000000013</v>
+        <v>99.14400000000002</v>
       </c>
       <c r="D415" s="4"/>
     </row>
@@ -13474,10 +13474,10 @@
         <v>26</v>
       </c>
       <c r="B416" s="10">
-        <v>99.083100000000016</v>
+        <v>99.144100000000023</v>
       </c>
       <c r="C416" s="10">
-        <v>99.092900000000014</v>
+        <v>99.153900000000021</v>
       </c>
       <c r="D416" s="4"/>
     </row>
@@ -13486,10 +13486,10 @@
         <v>27</v>
       </c>
       <c r="B417" s="9">
-        <v>99.093000000000018</v>
+        <v>99.154000000000025</v>
       </c>
       <c r="C417" s="9">
-        <v>99.093000000000018</v>
+        <v>99.154000000000025</v>
       </c>
       <c r="D417" s="4"/>
     </row>
@@ -13498,10 +13498,10 @@
         <v>26</v>
       </c>
       <c r="B418" s="10">
-        <v>99.093100000000021</v>
+        <v>99.154100000000028</v>
       </c>
       <c r="C418" s="10">
-        <v>99.10290000000002</v>
+        <v>99.163900000000027</v>
       </c>
       <c r="D418" s="4"/>
     </row>
@@ -13510,10 +13510,10 @@
         <v>27</v>
       </c>
       <c r="B419" s="9">
-        <v>99.103000000000023</v>
+        <v>99.16400000000003</v>
       </c>
       <c r="C419" s="9">
-        <v>99.103000000000023</v>
+        <v>99.16400000000003</v>
       </c>
       <c r="D419" s="4"/>
     </row>
@@ -13522,10 +13522,10 @@
         <v>26</v>
       </c>
       <c r="B420" s="10">
-        <v>99.103100000000026</v>
+        <v>99.164100000000033</v>
       </c>
       <c r="C420" s="10">
-        <v>99.113900000000001</v>
+        <v>99.173900000000032</v>
       </c>
       <c r="D420" s="4"/>
     </row>
@@ -13534,10 +13534,10 @@
         <v>27</v>
       </c>
       <c r="B421" s="9">
-        <v>99.114000000000004</v>
+        <v>99.174000000000035</v>
       </c>
       <c r="C421" s="9">
-        <v>99.114000000000004</v>
+        <v>99.174000000000035</v>
       </c>
       <c r="D421" s="4"/>
     </row>
@@ -13546,10 +13546,10 @@
         <v>26</v>
       </c>
       <c r="B422" s="10">
-        <v>99.114100000000008</v>
+        <v>99.174100000000038</v>
       </c>
       <c r="C422" s="10">
-        <v>99.123900000000006</v>
+        <v>99.183900000000037</v>
       </c>
       <c r="D422" s="4"/>
     </row>
@@ -13558,10 +13558,10 @@
         <v>27</v>
       </c>
       <c r="B423" s="9">
-        <v>99.124000000000009</v>
+        <v>99.18400000000004</v>
       </c>
       <c r="C423" s="9">
-        <v>99.124000000000009</v>
+        <v>99.18400000000004</v>
       </c>
       <c r="D423" s="4"/>
     </row>
@@ -13570,10 +13570,10 @@
         <v>26</v>
       </c>
       <c r="B424" s="10">
-        <v>99.124100000000013</v>
+        <v>99.184100000000043</v>
       </c>
       <c r="C424" s="10">
-        <v>99.133900000000011</v>
+        <v>99.193900000000042</v>
       </c>
       <c r="D424" s="4"/>
     </row>
@@ -13582,10 +13582,10 @@
         <v>27</v>
       </c>
       <c r="B425" s="9">
-        <v>99.134000000000015</v>
+        <v>99.194000000000045</v>
       </c>
       <c r="C425" s="9">
-        <v>99.134000000000015</v>
+        <v>99.194000000000045</v>
       </c>
       <c r="D425" s="4"/>
     </row>
@@ -13594,10 +13594,10 @@
         <v>26</v>
       </c>
       <c r="B426" s="10">
-        <v>99.134100000000018</v>
+        <v>99.194100000000049</v>
       </c>
       <c r="C426" s="10">
-        <v>99.143900000000016</v>
+        <v>99.20389999999999</v>
       </c>
       <c r="D426" s="4"/>
     </row>
@@ -13606,10 +13606,10 @@
         <v>27</v>
       </c>
       <c r="B427" s="9">
-        <v>99.14400000000002</v>
+        <v>99.203999999999994</v>
       </c>
       <c r="C427" s="9">
-        <v>99.14400000000002</v>
+        <v>99.203999999999994</v>
       </c>
       <c r="D427" s="4"/>
     </row>
@@ -13618,10 +13618,10 @@
         <v>26</v>
       </c>
       <c r="B428" s="10">
-        <v>99.144100000000023</v>
+        <v>99.204099999999997</v>
       </c>
       <c r="C428" s="10">
-        <v>99.153900000000021</v>
+        <v>99.213899999999995</v>
       </c>
       <c r="D428" s="4"/>
     </row>
@@ -13630,10 +13630,10 @@
         <v>27</v>
       </c>
       <c r="B429" s="9">
-        <v>99.154000000000025</v>
+        <v>99.213999999999999</v>
       </c>
       <c r="C429" s="9">
-        <v>99.154000000000025</v>
+        <v>99.213999999999999</v>
       </c>
       <c r="D429" s="4"/>
     </row>
@@ -13642,10 +13642,10 @@
         <v>26</v>
       </c>
       <c r="B430" s="10">
-        <v>99.154100000000028</v>
+        <v>99.214100000000002</v>
       </c>
       <c r="C430" s="10">
-        <v>99.163900000000027</v>
+        <v>99.221899999999991</v>
       </c>
       <c r="D430" s="4"/>
     </row>
@@ -13654,10 +13654,10 @@
         <v>27</v>
       </c>
       <c r="B431" s="9">
-        <v>99.16400000000003</v>
+        <v>99.221999999999994</v>
       </c>
       <c r="C431" s="9">
-        <v>99.16400000000003</v>
+        <v>99.221999999999994</v>
       </c>
       <c r="D431" s="4"/>
     </row>
@@ -13666,10 +13666,10 @@
         <v>26</v>
       </c>
       <c r="B432" s="10">
-        <v>99.164100000000033</v>
+        <v>99.222099999999998</v>
       </c>
       <c r="C432" s="10">
-        <v>99.173900000000032</v>
+        <v>99.2239</v>
       </c>
       <c r="D432" s="4"/>
     </row>
@@ -13678,10 +13678,10 @@
         <v>27</v>
       </c>
       <c r="B433" s="9">
-        <v>99.174000000000035</v>
+        <v>99.222999999999999</v>
       </c>
       <c r="C433" s="9">
-        <v>99.174000000000035</v>
+        <v>99.222999999999999</v>
       </c>
       <c r="D433" s="4"/>
     </row>
@@ -13690,10 +13690,10 @@
         <v>26</v>
       </c>
       <c r="B434" s="10">
-        <v>99.174100000000038</v>
+        <v>99.223100000000002</v>
       </c>
       <c r="C434" s="10">
-        <v>99.183900000000037</v>
+        <v>99.2239</v>
       </c>
       <c r="D434" s="4"/>
     </row>
@@ -13702,10 +13702,10 @@
         <v>27</v>
       </c>
       <c r="B435" s="9">
-        <v>99.18400000000004</v>
+        <v>99.224000000000004</v>
       </c>
       <c r="C435" s="9">
-        <v>99.18400000000004</v>
+        <v>99.224000000000004</v>
       </c>
       <c r="D435" s="4"/>
     </row>
@@ -13714,10 +13714,10 @@
         <v>26</v>
       </c>
       <c r="B436" s="10">
-        <v>99.184100000000043</v>
+        <v>99.224100000000007</v>
       </c>
       <c r="C436" s="10">
-        <v>99.193900000000042</v>
+        <v>99.224900000000005</v>
       </c>
       <c r="D436" s="4"/>
     </row>
@@ -13726,10 +13726,10 @@
         <v>27</v>
       </c>
       <c r="B437" s="9">
-        <v>99.194000000000045</v>
+        <v>99.224999999999994</v>
       </c>
       <c r="C437" s="9">
-        <v>99.194000000000045</v>
+        <v>99.224999999999994</v>
       </c>
       <c r="D437" s="4"/>
     </row>
@@ -13738,10 +13738,10 @@
         <v>26</v>
       </c>
       <c r="B438" s="10">
-        <v>99.194100000000049</v>
+        <v>99.225099999999998</v>
       </c>
       <c r="C438" s="10">
-        <v>99.20389999999999</v>
+        <v>99.235900000000001</v>
       </c>
       <c r="D438" s="4"/>
     </row>
@@ -13750,10 +13750,10 @@
         <v>27</v>
       </c>
       <c r="B439" s="9">
-        <v>99.203999999999994</v>
+        <v>99.236000000000004</v>
       </c>
       <c r="C439" s="9">
-        <v>99.203999999999994</v>
+        <v>99.236000000000004</v>
       </c>
       <c r="D439" s="4"/>
     </row>
@@ -13762,10 +13762,10 @@
         <v>26</v>
       </c>
       <c r="B440" s="10">
-        <v>99.204099999999997</v>
+        <v>99.236100000000008</v>
       </c>
       <c r="C440" s="10">
-        <v>99.213899999999995</v>
+        <v>99.245900000000006</v>
       </c>
       <c r="D440" s="4"/>
     </row>
@@ -13774,10 +13774,10 @@
         <v>27</v>
       </c>
       <c r="B441" s="9">
-        <v>99.213999999999999</v>
+        <v>99.246000000000009</v>
       </c>
       <c r="C441" s="9">
-        <v>99.213999999999999</v>
+        <v>99.246000000000009</v>
       </c>
       <c r="D441" s="4"/>
     </row>
@@ -13786,10 +13786,10 @@
         <v>26</v>
       </c>
       <c r="B442" s="10">
-        <v>99.214100000000002</v>
+        <v>99.246100000000013</v>
       </c>
       <c r="C442" s="10">
-        <v>99.221899999999991</v>
+        <v>99.255900000000011</v>
       </c>
       <c r="D442" s="4"/>
     </row>
@@ -13798,10 +13798,10 @@
         <v>27</v>
       </c>
       <c r="B443" s="9">
-        <v>99.221999999999994</v>
+        <v>99.256000000000014</v>
       </c>
       <c r="C443" s="9">
-        <v>99.221999999999994</v>
+        <v>99.256000000000014</v>
       </c>
       <c r="D443" s="4"/>
     </row>
@@ -13810,10 +13810,10 @@
         <v>26</v>
       </c>
       <c r="B444" s="10">
-        <v>99.222099999999998</v>
+        <v>99.256100000000018</v>
       </c>
       <c r="C444" s="10">
-        <v>99.2239</v>
+        <v>99.265900000000016</v>
       </c>
       <c r="D444" s="4"/>
     </row>
@@ -13822,10 +13822,10 @@
         <v>27</v>
       </c>
       <c r="B445" s="9">
-        <v>99.224000000000004</v>
+        <v>99.26600000000002</v>
       </c>
       <c r="C445" s="9">
-        <v>99.224000000000004</v>
+        <v>99.26600000000002</v>
       </c>
       <c r="D445" s="4"/>
     </row>
@@ -13834,10 +13834,10 @@
         <v>26</v>
       </c>
       <c r="B446" s="10">
-        <v>99.224100000000007</v>
+        <v>99.266100000000023</v>
       </c>
       <c r="C446" s="10">
-        <v>99.222899999999996</v>
+        <v>99.275900000000021</v>
       </c>
       <c r="D446" s="4"/>
     </row>
@@ -13846,10 +13846,10 @@
         <v>27</v>
       </c>
       <c r="B447" s="9">
-        <v>99.222999999999999</v>
+        <v>99.276000000000025</v>
       </c>
       <c r="C447" s="9">
-        <v>99.222999999999999</v>
+        <v>99.276000000000025</v>
       </c>
       <c r="D447" s="4"/>
     </row>
@@ -13858,10 +13858,10 @@
         <v>26</v>
       </c>
       <c r="B448" s="10">
-        <v>99.223100000000002</v>
+        <v>99.276100000000028</v>
       </c>
       <c r="C448" s="10">
-        <v>99.224899999999991</v>
+        <v>99.285900000000026</v>
       </c>
       <c r="D448" s="4"/>
     </row>
@@ -13870,10 +13870,10 @@
         <v>27</v>
       </c>
       <c r="B449" s="9">
-        <v>99.224999999999994</v>
+        <v>99.28600000000003</v>
       </c>
       <c r="C449" s="9">
-        <v>99.224999999999994</v>
+        <v>99.28600000000003</v>
       </c>
       <c r="D449" s="4"/>
     </row>
@@ -13882,10 +13882,10 @@
         <v>26</v>
       </c>
       <c r="B450" s="10">
-        <v>99.225099999999998</v>
+        <v>99.286100000000033</v>
       </c>
       <c r="C450" s="10">
-        <v>99.235900000000001</v>
+        <v>99.295900000000032</v>
       </c>
       <c r="D450" s="4"/>
     </row>
@@ -13894,10 +13894,10 @@
         <v>27</v>
       </c>
       <c r="B451" s="9">
-        <v>99.236000000000004</v>
+        <v>99.296000000000035</v>
       </c>
       <c r="C451" s="9">
-        <v>99.236000000000004</v>
+        <v>99.296000000000035</v>
       </c>
       <c r="D451" s="4"/>
     </row>
@@ -13906,10 +13906,10 @@
         <v>26</v>
       </c>
       <c r="B452" s="10">
-        <v>99.236100000000008</v>
+        <v>99.296100000000038</v>
       </c>
       <c r="C452" s="10">
-        <v>99.245900000000006</v>
+        <v>99.305900000000037</v>
       </c>
       <c r="D452" s="4"/>
     </row>
@@ -13918,10 +13918,10 @@
         <v>27</v>
       </c>
       <c r="B453" s="9">
-        <v>99.246000000000009</v>
+        <v>99.30600000000004</v>
       </c>
       <c r="C453" s="9">
-        <v>99.246000000000009</v>
+        <v>99.30600000000004</v>
       </c>
       <c r="D453" s="4"/>
     </row>
@@ -13930,10 +13930,10 @@
         <v>26</v>
       </c>
       <c r="B454" s="10">
-        <v>99.246100000000013</v>
+        <v>99.306100000000043</v>
       </c>
       <c r="C454" s="10">
-        <v>99.255900000000011</v>
+        <v>99.315900000000042</v>
       </c>
       <c r="D454" s="4"/>
     </row>
@@ -13942,10 +13942,10 @@
         <v>27</v>
       </c>
       <c r="B455" s="9">
-        <v>99.256000000000014</v>
+        <v>99.316000000000045</v>
       </c>
       <c r="C455" s="9">
-        <v>99.256000000000014</v>
+        <v>99.316000000000045</v>
       </c>
       <c r="D455" s="4"/>
     </row>
@@ -13954,10 +13954,10 @@
         <v>26</v>
       </c>
       <c r="B456" s="10">
-        <v>99.256100000000018</v>
+        <v>99.316100000000048</v>
       </c>
       <c r="C456" s="10">
-        <v>99.265900000000016</v>
+        <v>99.32589999999999</v>
       </c>
       <c r="D456" s="4"/>
     </row>
@@ -13966,10 +13966,10 @@
         <v>27</v>
       </c>
       <c r="B457" s="9">
-        <v>99.26600000000002</v>
+        <v>99.325999999999993</v>
       </c>
       <c r="C457" s="9">
-        <v>99.26600000000002</v>
+        <v>99.325999999999993</v>
       </c>
       <c r="D457" s="4"/>
     </row>
@@ -13978,10 +13978,10 @@
         <v>26</v>
       </c>
       <c r="B458" s="10">
-        <v>99.266100000000023</v>
+        <v>99.326099999999997</v>
       </c>
       <c r="C458" s="10">
-        <v>99.275900000000021</v>
+        <v>99.335899999999995</v>
       </c>
       <c r="D458" s="4"/>
     </row>
@@ -13990,10 +13990,10 @@
         <v>27</v>
       </c>
       <c r="B459" s="9">
-        <v>99.276000000000025</v>
+        <v>99.335999999999999</v>
       </c>
       <c r="C459" s="9">
-        <v>99.276000000000025</v>
+        <v>99.335999999999999</v>
       </c>
       <c r="D459" s="4"/>
     </row>
@@ -14002,10 +14002,10 @@
         <v>26</v>
       </c>
       <c r="B460" s="10">
-        <v>99.276100000000028</v>
+        <v>99.336100000000002</v>
       </c>
       <c r="C460" s="10">
-        <v>99.285900000000026</v>
+        <v>99.3459</v>
       </c>
       <c r="D460" s="4"/>
     </row>
@@ -14014,10 +14014,10 @@
         <v>27</v>
       </c>
       <c r="B461" s="9">
-        <v>99.28600000000003</v>
+        <v>99.346000000000004</v>
       </c>
       <c r="C461" s="9">
-        <v>99.28600000000003</v>
+        <v>99.346000000000004</v>
       </c>
       <c r="D461" s="4"/>
     </row>
@@ -14026,10 +14026,10 @@
         <v>26</v>
       </c>
       <c r="B462" s="10">
-        <v>99.286100000000033</v>
+        <v>99.346100000000007</v>
       </c>
       <c r="C462" s="10">
-        <v>99.295900000000032</v>
+        <v>99.355899999999991</v>
       </c>
       <c r="D462" s="4"/>
     </row>
@@ -14038,10 +14038,10 @@
         <v>27</v>
       </c>
       <c r="B463" s="9">
-        <v>99.296000000000035</v>
+        <v>99.355999999999995</v>
       </c>
       <c r="C463" s="9">
-        <v>99.296000000000035</v>
+        <v>99.355999999999995</v>
       </c>
       <c r="D463" s="4"/>
     </row>
@@ -14050,10 +14050,10 @@
         <v>26</v>
       </c>
       <c r="B464" s="10">
-        <v>99.296100000000038</v>
+        <v>99.356099999999998</v>
       </c>
       <c r="C464" s="10">
-        <v>99.305900000000037</v>
+        <v>99.358899999999991</v>
       </c>
       <c r="D464" s="4"/>
     </row>
@@ -14062,10 +14062,10 @@
         <v>27</v>
       </c>
       <c r="B465" s="9">
-        <v>99.30600000000004</v>
+        <v>99.358999999999995</v>
       </c>
       <c r="C465" s="9">
-        <v>99.30600000000004</v>
+        <v>99.358999999999995</v>
       </c>
       <c r="D465" s="4"/>
     </row>
@@ -14074,10 +14074,10 @@
         <v>26</v>
       </c>
       <c r="B466" s="10">
-        <v>99.306100000000043</v>
+        <v>99.359099999999998</v>
       </c>
       <c r="C466" s="10">
-        <v>99.315900000000042</v>
+        <v>99.368899999999996</v>
       </c>
       <c r="D466" s="4"/>
     </row>
@@ -14086,10 +14086,10 @@
         <v>27</v>
       </c>
       <c r="B467" s="9">
-        <v>99.316000000000045</v>
+        <v>99.369</v>
       </c>
       <c r="C467" s="9">
-        <v>99.316000000000045</v>
+        <v>99.369</v>
       </c>
       <c r="D467" s="4"/>
     </row>
@@ -14098,10 +14098,10 @@
         <v>26</v>
       </c>
       <c r="B468" s="10">
-        <v>99.316100000000048</v>
+        <v>99.369100000000003</v>
       </c>
       <c r="C468" s="10">
-        <v>99.32589999999999</v>
+        <v>99.377899999999997</v>
       </c>
       <c r="D468" s="4"/>
     </row>
@@ -14110,10 +14110,10 @@
         <v>27</v>
       </c>
       <c r="B469" s="9">
-        <v>99.325999999999993</v>
+        <v>99.378</v>
       </c>
       <c r="C469" s="9">
-        <v>99.325999999999993</v>
+        <v>99.378</v>
       </c>
       <c r="D469" s="4"/>
     </row>
@@ -14122,10 +14122,10 @@
         <v>26</v>
       </c>
       <c r="B470" s="10">
-        <v>99.326099999999997</v>
+        <v>99.378100000000003</v>
       </c>
       <c r="C470" s="10">
-        <v>99.335899999999995</v>
+        <v>99.384900000000002</v>
       </c>
       <c r="D470" s="4"/>
     </row>
@@ -14134,10 +14134,10 @@
         <v>27</v>
       </c>
       <c r="B471" s="9">
-        <v>99.335999999999999</v>
+        <v>99.385000000000005</v>
       </c>
       <c r="C471" s="9">
-        <v>99.335999999999999</v>
+        <v>99.385000000000005</v>
       </c>
       <c r="D471" s="4"/>
     </row>
@@ -14146,10 +14146,10 @@
         <v>26</v>
       </c>
       <c r="B472" s="10">
-        <v>99.336100000000002</v>
+        <v>99.385100000000008</v>
       </c>
       <c r="C472" s="10">
-        <v>99.3459</v>
+        <v>99.393900000000002</v>
       </c>
       <c r="D472" s="4"/>
     </row>
@@ -14158,10 +14158,10 @@
         <v>27</v>
       </c>
       <c r="B473" s="9">
-        <v>99.346000000000004</v>
+        <v>99.394000000000005</v>
       </c>
       <c r="C473" s="9">
-        <v>99.346000000000004</v>
+        <v>99.394000000000005</v>
       </c>
       <c r="D473" s="4"/>
     </row>
@@ -14170,10 +14170,10 @@
         <v>26</v>
       </c>
       <c r="B474" s="10">
-        <v>99.346100000000007</v>
+        <v>99.394100000000009</v>
       </c>
       <c r="C474" s="10">
-        <v>99.355899999999991</v>
+        <v>99.403899999999993</v>
       </c>
       <c r="D474" s="4"/>
     </row>
@@ -14182,10 +14182,10 @@
         <v>27</v>
       </c>
       <c r="B475" s="9">
-        <v>99.355999999999995</v>
+        <v>99.403999999999996</v>
       </c>
       <c r="C475" s="9">
-        <v>99.355999999999995</v>
+        <v>99.403999999999996</v>
       </c>
       <c r="D475" s="4"/>
     </row>
@@ -14194,10 +14194,10 @@
         <v>26</v>
       </c>
       <c r="B476" s="10">
-        <v>99.356099999999998</v>
+        <v>99.4041</v>
       </c>
       <c r="C476" s="10">
-        <v>99.358899999999991</v>
+        <v>99.413899999999998</v>
       </c>
       <c r="D476" s="4"/>
     </row>
@@ -14206,10 +14206,10 @@
         <v>27</v>
       </c>
       <c r="B477" s="9">
-        <v>99.358999999999995</v>
+        <v>99.414000000000001</v>
       </c>
       <c r="C477" s="9">
-        <v>99.358999999999995</v>
+        <v>99.414000000000001</v>
       </c>
       <c r="D477" s="4"/>
     </row>
@@ -14218,10 +14218,10 @@
         <v>26</v>
       </c>
       <c r="B478" s="10">
-        <v>99.359099999999998</v>
+        <v>99.414100000000005</v>
       </c>
       <c r="C478" s="10">
-        <v>99.368899999999996</v>
+        <v>99.422899999999998</v>
       </c>
       <c r="D478" s="4"/>
     </row>
@@ -14230,10 +14230,10 @@
         <v>27</v>
       </c>
       <c r="B479" s="9">
-        <v>99.369</v>
+        <v>99.423000000000002</v>
       </c>
       <c r="C479" s="9">
-        <v>99.369</v>
+        <v>99.423000000000002</v>
       </c>
       <c r="D479" s="4"/>
     </row>
@@ -14242,10 +14242,10 @@
         <v>26</v>
       </c>
       <c r="B480" s="10">
-        <v>99.369100000000003</v>
+        <v>99.423100000000005</v>
       </c>
       <c r="C480" s="10">
-        <v>99.377899999999997</v>
+        <v>99.432900000000004</v>
       </c>
       <c r="D480" s="4"/>
     </row>
@@ -14254,10 +14254,10 @@
         <v>27</v>
       </c>
       <c r="B481" s="9">
-        <v>99.378</v>
+        <v>99.433000000000007</v>
       </c>
       <c r="C481" s="9">
-        <v>99.378</v>
+        <v>99.433000000000007</v>
       </c>
       <c r="D481" s="4"/>
     </row>
@@ -14266,10 +14266,10 @@
         <v>26</v>
       </c>
       <c r="B482" s="10">
-        <v>99.378100000000003</v>
+        <v>99.43310000000001</v>
       </c>
       <c r="C482" s="10">
-        <v>99.384900000000002</v>
+        <v>99.442900000000009</v>
       </c>
       <c r="D482" s="4"/>
     </row>
@@ -14278,10 +14278,10 @@
         <v>27</v>
       </c>
       <c r="B483" s="9">
-        <v>99.385000000000005</v>
+        <v>99.443000000000012</v>
       </c>
       <c r="C483" s="9">
-        <v>99.385000000000005</v>
+        <v>99.443000000000012</v>
       </c>
       <c r="D483" s="4"/>
     </row>
@@ -14290,10 +14290,10 @@
         <v>26</v>
       </c>
       <c r="B484" s="10">
-        <v>99.385100000000008</v>
+        <v>99.443100000000015</v>
       </c>
       <c r="C484" s="10">
-        <v>99.393900000000002</v>
+        <v>99.452900000000014</v>
       </c>
       <c r="D484" s="4"/>
     </row>
@@ -14302,10 +14302,10 @@
         <v>27</v>
       </c>
       <c r="B485" s="9">
-        <v>99.394000000000005</v>
+        <v>99.453000000000017</v>
       </c>
       <c r="C485" s="9">
-        <v>99.394000000000005</v>
+        <v>99.453000000000017</v>
       </c>
       <c r="D485" s="4"/>
     </row>
@@ -14314,10 +14314,10 @@
         <v>26</v>
       </c>
       <c r="B486" s="10">
-        <v>99.394100000000009</v>
+        <v>99.45310000000002</v>
       </c>
       <c r="C486" s="10">
-        <v>99.403899999999993</v>
+        <v>99.462900000000019</v>
       </c>
       <c r="D486" s="4"/>
     </row>
@@ -14326,10 +14326,10 @@
         <v>27</v>
       </c>
       <c r="B487" s="9">
-        <v>99.403999999999996</v>
+        <v>99.463000000000022</v>
       </c>
       <c r="C487" s="9">
-        <v>99.403999999999996</v>
+        <v>99.463000000000022</v>
       </c>
       <c r="D487" s="4"/>
     </row>
@@ -14338,10 +14338,10 @@
         <v>26</v>
       </c>
       <c r="B488" s="10">
-        <v>99.4041</v>
+        <v>99.463100000000026</v>
       </c>
       <c r="C488" s="10">
-        <v>99.413899999999998</v>
+        <v>99.472900000000024</v>
       </c>
       <c r="D488" s="4"/>
     </row>
@@ -14350,10 +14350,10 @@
         <v>27</v>
       </c>
       <c r="B489" s="9">
-        <v>99.414000000000001</v>
+        <v>99.473000000000027</v>
       </c>
       <c r="C489" s="9">
-        <v>99.414000000000001</v>
+        <v>99.473000000000027</v>
       </c>
       <c r="D489" s="4"/>
     </row>
@@ -14362,10 +14362,10 @@
         <v>26</v>
       </c>
       <c r="B490" s="10">
-        <v>99.414100000000005</v>
+        <v>99.473100000000031</v>
       </c>
       <c r="C490" s="10">
-        <v>99.422899999999998</v>
+        <v>99.482900000000029</v>
       </c>
       <c r="D490" s="4"/>
     </row>
@@ -14374,10 +14374,10 @@
         <v>27</v>
       </c>
       <c r="B491" s="9">
-        <v>99.423000000000002</v>
+        <v>99.483000000000033</v>
       </c>
       <c r="C491" s="9">
-        <v>99.423000000000002</v>
+        <v>99.483000000000033</v>
       </c>
       <c r="D491" s="4"/>
     </row>
@@ -14386,10 +14386,10 @@
         <v>26</v>
       </c>
       <c r="B492" s="10">
-        <v>99.423100000000005</v>
+        <v>99.483100000000036</v>
       </c>
       <c r="C492" s="10">
-        <v>99.432900000000004</v>
+        <v>99.492900000000034</v>
       </c>
       <c r="D492" s="4"/>
     </row>
@@ -14398,10 +14398,10 @@
         <v>27</v>
       </c>
       <c r="B493" s="9">
-        <v>99.433000000000007</v>
+        <v>99.493000000000038</v>
       </c>
       <c r="C493" s="9">
-        <v>99.433000000000007</v>
+        <v>99.493000000000038</v>
       </c>
       <c r="D493" s="4"/>
     </row>
@@ -14410,10 +14410,10 @@
         <v>26</v>
       </c>
       <c r="B494" s="10">
-        <v>99.43310000000001</v>
+        <v>99.493100000000041</v>
       </c>
       <c r="C494" s="10">
-        <v>99.442900000000009</v>
+        <v>99.502900000000039</v>
       </c>
       <c r="D494" s="4"/>
     </row>
@@ -14422,10 +14422,10 @@
         <v>27</v>
       </c>
       <c r="B495" s="9">
-        <v>99.443000000000012</v>
+        <v>99.503000000000043</v>
       </c>
       <c r="C495" s="9">
-        <v>99.443000000000012</v>
+        <v>99.503000000000043</v>
       </c>
       <c r="D495" s="4"/>
     </row>
@@ -14434,10 +14434,10 @@
         <v>26</v>
       </c>
       <c r="B496" s="10">
-        <v>99.443100000000015</v>
+        <v>99.503100000000046</v>
       </c>
       <c r="C496" s="10">
-        <v>99.452900000000014</v>
+        <v>99.512900000000045</v>
       </c>
       <c r="D496" s="4"/>
     </row>
@@ -14446,10 +14446,10 @@
         <v>27</v>
       </c>
       <c r="B497" s="9">
-        <v>99.453000000000017</v>
+        <v>99.513000000000048</v>
       </c>
       <c r="C497" s="9">
-        <v>99.453000000000017</v>
+        <v>99.513000000000048</v>
       </c>
       <c r="D497" s="4"/>
     </row>
@@ -14458,10 +14458,10 @@
         <v>26</v>
       </c>
       <c r="B498" s="10">
-        <v>99.45310000000002</v>
+        <v>99.513100000000051</v>
       </c>
       <c r="C498" s="10">
-        <v>99.462900000000019</v>
+        <v>99.522899999999993</v>
       </c>
       <c r="D498" s="4"/>
     </row>
@@ -14470,10 +14470,10 @@
         <v>27</v>
       </c>
       <c r="B499" s="9">
-        <v>99.463000000000022</v>
+        <v>99.522999999999996</v>
       </c>
       <c r="C499" s="9">
-        <v>99.463000000000022</v>
+        <v>99.522999999999996</v>
       </c>
       <c r="D499" s="4"/>
     </row>
@@ -14482,10 +14482,10 @@
         <v>26</v>
       </c>
       <c r="B500" s="10">
-        <v>99.463100000000026</v>
+        <v>99.523099999999999</v>
       </c>
       <c r="C500" s="10">
-        <v>99.472900000000024</v>
+        <v>99.532899999999998</v>
       </c>
       <c r="D500" s="4"/>
     </row>
@@ -14494,10 +14494,10 @@
         <v>27</v>
       </c>
       <c r="B501" s="9">
-        <v>99.473000000000027</v>
+        <v>99.533000000000001</v>
       </c>
       <c r="C501" s="9">
-        <v>99.473000000000027</v>
+        <v>99.533000000000001</v>
       </c>
       <c r="D501" s="4"/>
     </row>
@@ -14506,10 +14506,10 @@
         <v>26</v>
       </c>
       <c r="B502" s="10">
-        <v>99.473100000000031</v>
+        <v>99.533100000000005</v>
       </c>
       <c r="C502" s="10">
-        <v>99.482900000000029</v>
+        <v>99.542900000000003</v>
       </c>
       <c r="D502" s="4"/>
     </row>
@@ -14518,10 +14518,10 @@
         <v>27</v>
       </c>
       <c r="B503" s="9">
-        <v>99.483000000000033</v>
+        <v>99.543000000000006</v>
       </c>
       <c r="C503" s="9">
-        <v>99.483000000000033</v>
+        <v>99.543000000000006</v>
       </c>
       <c r="D503" s="4"/>
     </row>
@@ -14530,10 +14530,10 @@
         <v>26</v>
       </c>
       <c r="B504" s="10">
-        <v>99.483100000000036</v>
+        <v>99.54310000000001</v>
       </c>
       <c r="C504" s="10">
-        <v>99.492900000000034</v>
+        <v>99.552899999999994</v>
       </c>
       <c r="D504" s="4"/>
     </row>
@@ -14542,10 +14542,10 @@
         <v>27</v>
       </c>
       <c r="B505" s="9">
-        <v>99.493000000000038</v>
+        <v>99.552999999999997</v>
       </c>
       <c r="C505" s="9">
-        <v>99.493000000000038</v>
+        <v>99.552999999999997</v>
       </c>
       <c r="D505" s="4"/>
     </row>
@@ -14554,10 +14554,10 @@
         <v>26</v>
       </c>
       <c r="B506" s="10">
-        <v>99.493100000000041</v>
+        <v>99.553100000000001</v>
       </c>
       <c r="C506" s="10">
-        <v>99.502900000000039</v>
+        <v>99.562899999999999</v>
       </c>
       <c r="D506" s="4"/>
     </row>
@@ -14566,10 +14566,10 @@
         <v>27</v>
       </c>
       <c r="B507" s="9">
-        <v>99.503000000000043</v>
+        <v>99.563000000000002</v>
       </c>
       <c r="C507" s="9">
-        <v>99.503000000000043</v>
+        <v>99.563000000000002</v>
       </c>
       <c r="D507" s="4"/>
     </row>
@@ -14578,10 +14578,10 @@
         <v>26</v>
       </c>
       <c r="B508" s="10">
-        <v>99.503100000000046</v>
+        <v>99.563100000000006</v>
       </c>
       <c r="C508" s="10">
-        <v>99.512900000000045</v>
+        <v>99.57289999999999</v>
       </c>
       <c r="D508" s="4"/>
     </row>
@@ -14590,10 +14590,10 @@
         <v>27</v>
       </c>
       <c r="B509" s="9">
-        <v>99.513000000000048</v>
+        <v>99.572999999999993</v>
       </c>
       <c r="C509" s="9">
-        <v>99.513000000000048</v>
+        <v>99.572999999999993</v>
       </c>
       <c r="D509" s="4"/>
     </row>
@@ -14602,10 +14602,10 @@
         <v>26</v>
       </c>
       <c r="B510" s="10">
-        <v>99.513100000000051</v>
+        <v>99.573099999999997</v>
       </c>
       <c r="C510" s="10">
-        <v>99.522899999999993</v>
+        <v>99.582899999999995</v>
       </c>
       <c r="D510" s="4"/>
     </row>
@@ -14614,10 +14614,10 @@
         <v>27</v>
       </c>
       <c r="B511" s="9">
-        <v>99.522999999999996</v>
+        <v>99.582999999999998</v>
       </c>
       <c r="C511" s="9">
-        <v>99.522999999999996</v>
+        <v>99.582999999999998</v>
       </c>
       <c r="D511" s="4"/>
     </row>
@@ -14626,10 +14626,10 @@
         <v>26</v>
       </c>
       <c r="B512" s="10">
-        <v>99.523099999999999</v>
+        <v>99.583100000000002</v>
       </c>
       <c r="C512" s="10">
-        <v>99.532899999999998</v>
+        <v>99.5929</v>
       </c>
       <c r="D512" s="4"/>
     </row>
@@ -14638,10 +14638,10 @@
         <v>27</v>
       </c>
       <c r="B513" s="9">
-        <v>99.533000000000001</v>
+        <v>99.593000000000004</v>
       </c>
       <c r="C513" s="9">
-        <v>99.533000000000001</v>
+        <v>99.593000000000004</v>
       </c>
       <c r="D513" s="4"/>
     </row>
@@ -14650,10 +14650,10 @@
         <v>26</v>
       </c>
       <c r="B514" s="10">
-        <v>99.533100000000005</v>
+        <v>99.593100000000007</v>
       </c>
       <c r="C514" s="10">
-        <v>99.542900000000003</v>
+        <v>99.602899999999991</v>
       </c>
       <c r="D514" s="4"/>
     </row>
@@ -14662,10 +14662,10 @@
         <v>27</v>
       </c>
       <c r="B515" s="9">
-        <v>99.543000000000006</v>
+        <v>99.602999999999994</v>
       </c>
       <c r="C515" s="9">
-        <v>99.543000000000006</v>
+        <v>99.602999999999994</v>
       </c>
       <c r="D515" s="4"/>
     </row>
@@ -14674,10 +14674,10 @@
         <v>26</v>
       </c>
       <c r="B516" s="10">
-        <v>99.54310000000001</v>
+        <v>99.603099999999998</v>
       </c>
       <c r="C516" s="10">
-        <v>99.552899999999994</v>
+        <v>99.612899999999996</v>
       </c>
       <c r="D516" s="4"/>
     </row>
@@ -14686,10 +14686,10 @@
         <v>27</v>
       </c>
       <c r="B517" s="9">
-        <v>99.552999999999997</v>
+        <v>99.613</v>
       </c>
       <c r="C517" s="9">
-        <v>99.552999999999997</v>
+        <v>99.613</v>
       </c>
       <c r="D517" s="4"/>
     </row>
@@ -14698,10 +14698,10 @@
         <v>26</v>
       </c>
       <c r="B518" s="10">
-        <v>99.553100000000001</v>
+        <v>99.613100000000003</v>
       </c>
       <c r="C518" s="10">
-        <v>99.562899999999999</v>
+        <v>99.622900000000001</v>
       </c>
       <c r="D518" s="4"/>
     </row>
@@ -14710,10 +14710,10 @@
         <v>27</v>
       </c>
       <c r="B519" s="9">
-        <v>99.563000000000002</v>
+        <v>99.623000000000005</v>
       </c>
       <c r="C519" s="9">
-        <v>99.563000000000002</v>
+        <v>99.623000000000005</v>
       </c>
       <c r="D519" s="4"/>
     </row>
@@ -14722,10 +14722,10 @@
         <v>26</v>
       </c>
       <c r="B520" s="10">
-        <v>99.563100000000006</v>
+        <v>99.623100000000008</v>
       </c>
       <c r="C520" s="10">
-        <v>99.57289999999999</v>
+        <v>99.632899999999992</v>
       </c>
       <c r="D520" s="4"/>
     </row>
@@ -14734,10 +14734,10 @@
         <v>27</v>
       </c>
       <c r="B521" s="9">
-        <v>99.572999999999993</v>
+        <v>99.632999999999996</v>
       </c>
       <c r="C521" s="9">
-        <v>99.572999999999993</v>
+        <v>99.632999999999996</v>
       </c>
       <c r="D521" s="4"/>
     </row>
@@ -14746,10 +14746,10 @@
         <v>26</v>
       </c>
       <c r="B522" s="10">
-        <v>99.573099999999997</v>
+        <v>99.633099999999999</v>
       </c>
       <c r="C522" s="10">
-        <v>99.582899999999995</v>
+        <v>99.642899999999997</v>
       </c>
       <c r="D522" s="4"/>
     </row>
@@ -14758,10 +14758,10 @@
         <v>27</v>
       </c>
       <c r="B523" s="9">
-        <v>99.582999999999998</v>
+        <v>99.643000000000001</v>
       </c>
       <c r="C523" s="9">
-        <v>99.582999999999998</v>
+        <v>99.643000000000001</v>
       </c>
       <c r="D523" s="4"/>
     </row>
@@ -14770,10 +14770,10 @@
         <v>26</v>
       </c>
       <c r="B524" s="10">
-        <v>99.583100000000002</v>
+        <v>99.643100000000004</v>
       </c>
       <c r="C524" s="10">
-        <v>99.5929</v>
+        <v>99.652900000000002</v>
       </c>
       <c r="D524" s="4"/>
     </row>
@@ -14782,10 +14782,10 @@
         <v>27</v>
       </c>
       <c r="B525" s="9">
-        <v>99.593000000000004</v>
+        <v>99.653000000000006</v>
       </c>
       <c r="C525" s="9">
-        <v>99.593000000000004</v>
+        <v>99.653000000000006</v>
       </c>
       <c r="D525" s="4"/>
     </row>
@@ -14794,10 +14794,10 @@
         <v>26</v>
       </c>
       <c r="B526" s="10">
-        <v>99.593100000000007</v>
+        <v>99.653100000000009</v>
       </c>
       <c r="C526" s="10">
-        <v>99.602899999999991</v>
+        <v>99.662899999999993</v>
       </c>
       <c r="D526" s="4"/>
     </row>
@@ -14806,10 +14806,10 @@
         <v>27</v>
       </c>
       <c r="B527" s="9">
-        <v>99.602999999999994</v>
+        <v>99.662999999999997</v>
       </c>
       <c r="C527" s="9">
-        <v>99.602999999999994</v>
+        <v>99.662999999999997</v>
       </c>
       <c r="D527" s="4"/>
     </row>
@@ -14818,10 +14818,10 @@
         <v>26</v>
       </c>
       <c r="B528" s="10">
-        <v>99.603099999999998</v>
+        <v>99.6631</v>
       </c>
       <c r="C528" s="10">
-        <v>99.612899999999996</v>
+        <v>99.672899999999998</v>
       </c>
       <c r="D528" s="4"/>
     </row>
@@ -14830,10 +14830,10 @@
         <v>27</v>
       </c>
       <c r="B529" s="9">
-        <v>99.613</v>
+        <v>99.673000000000002</v>
       </c>
       <c r="C529" s="9">
-        <v>99.613</v>
+        <v>99.673000000000002</v>
       </c>
       <c r="D529" s="4"/>
     </row>
@@ -14842,10 +14842,10 @@
         <v>26</v>
       </c>
       <c r="B530" s="10">
-        <v>99.613100000000003</v>
+        <v>99.673100000000005</v>
       </c>
       <c r="C530" s="10">
-        <v>99.622900000000001</v>
+        <v>99.681899999999999</v>
       </c>
       <c r="D530" s="4"/>
     </row>
@@ -14854,10 +14854,10 @@
         <v>27</v>
       </c>
       <c r="B531" s="9">
-        <v>99.623000000000005</v>
+        <v>99.682000000000002</v>
       </c>
       <c r="C531" s="9">
-        <v>99.623000000000005</v>
+        <v>99.682000000000002</v>
       </c>
       <c r="D531" s="4"/>
     </row>
@@ -14866,10 +14866,10 @@
         <v>26</v>
       </c>
       <c r="B532" s="10">
-        <v>99.623100000000008</v>
+        <v>99.682100000000005</v>
       </c>
       <c r="C532" s="10">
-        <v>99.632899999999992</v>
+        <v>99.682900000000004</v>
       </c>
       <c r="D532" s="4"/>
     </row>
@@ -14878,10 +14878,10 @@
         <v>27</v>
       </c>
       <c r="B533" s="9">
-        <v>99.632999999999996</v>
+        <v>99.683000000000007</v>
       </c>
       <c r="C533" s="9">
-        <v>99.632999999999996</v>
+        <v>99.683000000000007</v>
       </c>
       <c r="D533" s="4"/>
     </row>
@@ -14890,10 +14890,10 @@
         <v>26</v>
       </c>
       <c r="B534" s="10">
-        <v>99.633099999999999</v>
+        <v>99.68310000000001</v>
       </c>
       <c r="C534" s="10">
-        <v>99.642899999999997</v>
+        <v>99.683899999999994</v>
       </c>
       <c r="D534" s="4"/>
     </row>
@@ -14902,10 +14902,10 @@
         <v>27</v>
       </c>
       <c r="B535" s="9">
-        <v>99.643000000000001</v>
+        <v>99.683999999999997</v>
       </c>
       <c r="C535" s="9">
-        <v>99.643000000000001</v>
+        <v>99.683999999999997</v>
       </c>
       <c r="D535" s="4"/>
     </row>
@@ -14914,10 +14914,10 @@
         <v>26</v>
       </c>
       <c r="B536" s="10">
-        <v>99.643100000000004</v>
+        <v>99.684100000000001</v>
       </c>
       <c r="C536" s="10">
-        <v>99.652900000000002</v>
+        <v>99.684899999999999</v>
       </c>
       <c r="D536" s="4"/>
     </row>
@@ -14926,10 +14926,10 @@
         <v>27</v>
       </c>
       <c r="B537" s="9">
-        <v>99.653000000000006</v>
+        <v>99.685000000000002</v>
       </c>
       <c r="C537" s="9">
-        <v>99.653000000000006</v>
+        <v>99.685000000000002</v>
       </c>
       <c r="D537" s="4"/>
     </row>
@@ -14938,10 +14938,10 @@
         <v>26</v>
       </c>
       <c r="B538" s="10">
-        <v>99.653100000000009</v>
+        <v>99.695099999999996</v>
       </c>
       <c r="C538" s="10">
-        <v>99.662899999999993</v>
+        <v>99.704899999999995</v>
       </c>
       <c r="D538" s="4"/>
     </row>
@@ -14950,10 +14950,10 @@
         <v>27</v>
       </c>
       <c r="B539" s="9">
-        <v>99.662999999999997</v>
+        <v>99.704999999999998</v>
       </c>
       <c r="C539" s="9">
-        <v>99.662999999999997</v>
+        <v>99.704999999999998</v>
       </c>
       <c r="D539" s="4"/>
     </row>
@@ -14962,10 +14962,10 @@
         <v>26</v>
       </c>
       <c r="B540" s="10">
-        <v>99.6631</v>
+        <v>99.705100000000002</v>
       </c>
       <c r="C540" s="10">
-        <v>99.672899999999998</v>
+        <v>99.7149</v>
       </c>
       <c r="D540" s="4"/>
     </row>
@@ -14974,10 +14974,10 @@
         <v>27</v>
       </c>
       <c r="B541" s="9">
-        <v>99.673000000000002</v>
+        <v>99.715000000000003</v>
       </c>
       <c r="C541" s="9">
-        <v>99.673000000000002</v>
+        <v>99.715000000000003</v>
       </c>
       <c r="D541" s="4"/>
     </row>
@@ -14986,10 +14986,10 @@
         <v>26</v>
       </c>
       <c r="B542" s="10">
-        <v>99.673100000000005</v>
+        <v>99.715100000000007</v>
       </c>
       <c r="C542" s="10">
-        <v>99.681899999999999</v>
+        <v>99.724899999999991</v>
       </c>
       <c r="D542" s="4"/>
     </row>
@@ -14998,10 +14998,10 @@
         <v>27</v>
       </c>
       <c r="B543" s="9">
-        <v>99.682000000000002</v>
+        <v>99.724999999999994</v>
       </c>
       <c r="C543" s="9">
-        <v>99.682000000000002</v>
+        <v>99.724999999999994</v>
       </c>
       <c r="D543" s="4"/>
     </row>
@@ -15010,10 +15010,10 @@
         <v>26</v>
       </c>
       <c r="B544" s="10">
-        <v>99.682100000000005</v>
+        <v>99.725099999999998</v>
       </c>
       <c r="C544" s="10">
-        <v>99.683899999999994</v>
+        <v>99.734899999999996</v>
       </c>
       <c r="D544" s="4"/>
     </row>
@@ -15022,10 +15022,10 @@
         <v>27</v>
       </c>
       <c r="B545" s="9">
-        <v>99.683999999999997</v>
+        <v>99.734999999999999</v>
       </c>
       <c r="C545" s="9">
-        <v>99.683999999999997</v>
+        <v>99.734999999999999</v>
       </c>
       <c r="D545" s="4"/>
     </row>
@@ -15034,10 +15034,10 @@
         <v>26</v>
       </c>
       <c r="B546" s="10">
-        <v>99.684100000000001</v>
+        <v>99.735100000000003</v>
       </c>
       <c r="C546" s="10">
-        <v>99.682900000000004</v>
+        <v>99.744900000000001</v>
       </c>
       <c r="D546" s="4"/>
     </row>
@@ -15046,10 +15046,10 @@
         <v>27</v>
       </c>
       <c r="B547" s="9">
-        <v>99.683000000000007</v>
+        <v>99.745000000000005</v>
       </c>
       <c r="C547" s="9">
-        <v>99.683000000000007</v>
+        <v>99.745000000000005</v>
       </c>
       <c r="D547" s="4"/>
     </row>
@@ -15058,10 +15058,10 @@
         <v>26</v>
       </c>
       <c r="B548" s="10">
-        <v>99.68310000000001</v>
+        <v>99.745100000000008</v>
       </c>
       <c r="C548" s="10">
-        <v>99.684899999999999</v>
+        <v>99.754899999999992</v>
       </c>
       <c r="D548" s="4"/>
     </row>
@@ -15070,10 +15070,10 @@
         <v>27</v>
       </c>
       <c r="B549" s="9">
-        <v>99.685000000000002</v>
+        <v>99.754999999999995</v>
       </c>
       <c r="C549" s="9">
-        <v>99.685000000000002</v>
+        <v>99.754999999999995</v>
       </c>
       <c r="D549" s="4"/>
     </row>
@@ -15082,10 +15082,10 @@
         <v>26</v>
       </c>
       <c r="B550" s="10">
-        <v>99.685100000000006</v>
+        <v>99.755099999999999</v>
       </c>
       <c r="C550" s="10">
-        <v>99.69489999999999</v>
+        <v>99.763899999999992</v>
       </c>
       <c r="D550" s="4"/>
     </row>
@@ -15094,10 +15094,10 @@
         <v>27</v>
       </c>
       <c r="B551" s="9">
-        <v>99.694999999999993</v>
+        <v>99.763999999999996</v>
       </c>
       <c r="C551" s="9">
-        <v>99.694999999999993</v>
+        <v>99.763999999999996</v>
       </c>
       <c r="D551" s="4"/>
     </row>
@@ -15106,10 +15106,10 @@
         <v>26</v>
       </c>
       <c r="B552" s="10">
-        <v>99.695099999999996</v>
+        <v>99.764099999999999</v>
       </c>
       <c r="C552" s="10">
-        <v>99.704899999999995</v>
+        <v>99.773899999999998</v>
       </c>
       <c r="D552" s="4"/>
     </row>
@@ -15118,10 +15118,10 @@
         <v>27</v>
       </c>
       <c r="B553" s="9">
-        <v>99.704999999999998</v>
+        <v>99.774000000000001</v>
       </c>
       <c r="C553" s="9">
-        <v>99.704999999999998</v>
+        <v>99.774000000000001</v>
       </c>
       <c r="D553" s="4"/>
     </row>
@@ -15130,10 +15130,10 @@
         <v>26</v>
       </c>
       <c r="B554" s="10">
-        <v>99.705100000000002</v>
+        <v>99.774100000000004</v>
       </c>
       <c r="C554" s="10">
-        <v>99.7149</v>
+        <v>99.783900000000003</v>
       </c>
       <c r="D554" s="4"/>
     </row>
@@ -15142,10 +15142,10 @@
         <v>27</v>
       </c>
       <c r="B555" s="9">
-        <v>99.715000000000003</v>
+        <v>99.784000000000006</v>
       </c>
       <c r="C555" s="9">
-        <v>99.715000000000003</v>
+        <v>99.784000000000006</v>
       </c>
       <c r="D555" s="4"/>
     </row>
@@ -15154,10 +15154,10 @@
         <v>26</v>
       </c>
       <c r="B556" s="10">
-        <v>99.715100000000007</v>
+        <v>99.784100000000009</v>
       </c>
       <c r="C556" s="10">
-        <v>99.724899999999991</v>
+        <v>99.793900000000008</v>
       </c>
       <c r="D556" s="4"/>
     </row>
@@ -15166,10 +15166,10 @@
         <v>27</v>
       </c>
       <c r="B557" s="9">
-        <v>99.724999999999994</v>
+        <v>99.794000000000011</v>
       </c>
       <c r="C557" s="9">
-        <v>99.724999999999994</v>
+        <v>99.794000000000011</v>
       </c>
       <c r="D557" s="4"/>
     </row>
@@ -15178,10 +15178,10 @@
         <v>26</v>
       </c>
       <c r="B558" s="10">
-        <v>99.725099999999998</v>
+        <v>99.794100000000014</v>
       </c>
       <c r="C558" s="10">
-        <v>99.734899999999996</v>
+        <v>99.803900000000013</v>
       </c>
       <c r="D558" s="4"/>
     </row>
@@ -15190,10 +15190,10 @@
         <v>27</v>
       </c>
       <c r="B559" s="9">
-        <v>99.734999999999999</v>
+        <v>99.804000000000016</v>
       </c>
       <c r="C559" s="9">
-        <v>99.734999999999999</v>
+        <v>99.804000000000016</v>
       </c>
       <c r="D559" s="4"/>
     </row>
@@ -15202,10 +15202,10 @@
         <v>26</v>
       </c>
       <c r="B560" s="10">
-        <v>99.735100000000003</v>
+        <v>99.80410000000002</v>
       </c>
       <c r="C560" s="10">
-        <v>99.744900000000001</v>
+        <v>99.813900000000018</v>
       </c>
       <c r="D560" s="4"/>
     </row>
@@ -15214,10 +15214,10 @@
         <v>27</v>
       </c>
       <c r="B561" s="9">
-        <v>99.745000000000005</v>
+        <v>99.814000000000021</v>
       </c>
       <c r="C561" s="9">
-        <v>99.745000000000005</v>
+        <v>99.814000000000021</v>
       </c>
       <c r="D561" s="4"/>
     </row>
@@ -15226,10 +15226,10 @@
         <v>26</v>
       </c>
       <c r="B562" s="10">
-        <v>99.745100000000008</v>
+        <v>99.814100000000025</v>
       </c>
       <c r="C562" s="10">
-        <v>99.754899999999992</v>
+        <v>99.823900000000023</v>
       </c>
       <c r="D562" s="4"/>
     </row>
@@ -15238,10 +15238,10 @@
         <v>27</v>
       </c>
       <c r="B563" s="9">
-        <v>99.754999999999995</v>
+        <v>99.824000000000026</v>
       </c>
       <c r="C563" s="9">
-        <v>99.754999999999995</v>
+        <v>99.824000000000026</v>
       </c>
       <c r="D563" s="4"/>
     </row>
@@ -15250,10 +15250,10 @@
         <v>26</v>
       </c>
       <c r="B564" s="10">
-        <v>99.755099999999999</v>
+        <v>99.82410000000003</v>
       </c>
       <c r="C564" s="10">
-        <v>99.763899999999992</v>
+        <v>99.833900000000028</v>
       </c>
       <c r="D564" s="4"/>
     </row>
@@ -15262,10 +15262,10 @@
         <v>27</v>
       </c>
       <c r="B565" s="9">
-        <v>99.763999999999996</v>
+        <v>99.834000000000032</v>
       </c>
       <c r="C565" s="9">
-        <v>99.763999999999996</v>
+        <v>99.834000000000032</v>
       </c>
       <c r="D565" s="4"/>
     </row>
@@ -15274,10 +15274,10 @@
         <v>26</v>
       </c>
       <c r="B566" s="10">
-        <v>99.764099999999999</v>
+        <v>99.834100000000035</v>
       </c>
       <c r="C566" s="10">
-        <v>99.773899999999998</v>
+        <v>99.843900000000033</v>
       </c>
       <c r="D566" s="4"/>
     </row>
@@ -15286,10 +15286,10 @@
         <v>27</v>
       </c>
       <c r="B567" s="9">
-        <v>99.774000000000001</v>
+        <v>99.844000000000037</v>
       </c>
       <c r="C567" s="9">
-        <v>99.774000000000001</v>
+        <v>99.844000000000037</v>
       </c>
       <c r="D567" s="4"/>
     </row>
@@ -15298,10 +15298,10 @@
         <v>26</v>
       </c>
       <c r="B568" s="10">
-        <v>99.774100000000004</v>
+        <v>99.84410000000004</v>
       </c>
       <c r="C568" s="10">
-        <v>99.783900000000003</v>
+        <v>99.853900000000039</v>
       </c>
       <c r="D568" s="4"/>
     </row>
@@ -15310,10 +15310,10 @@
         <v>27</v>
       </c>
       <c r="B569" s="9">
-        <v>99.784000000000006</v>
+        <v>99.854000000000042</v>
       </c>
       <c r="C569" s="9">
-        <v>99.784000000000006</v>
+        <v>99.854000000000042</v>
       </c>
       <c r="D569" s="4"/>
     </row>
@@ -15322,10 +15322,10 @@
         <v>26</v>
       </c>
       <c r="B570" s="10">
-        <v>99.784100000000009</v>
+        <v>99.854100000000045</v>
       </c>
       <c r="C570" s="10">
-        <v>99.793900000000008</v>
+        <v>99.863900000000044</v>
       </c>
       <c r="D570" s="4"/>
     </row>
@@ -15334,10 +15334,10 @@
         <v>27</v>
       </c>
       <c r="B571" s="9">
-        <v>99.794000000000011</v>
+        <v>99.864000000000047</v>
       </c>
       <c r="C571" s="9">
-        <v>99.794000000000011</v>
+        <v>99.864000000000047</v>
       </c>
       <c r="D571" s="4"/>
     </row>
@@ -15346,10 +15346,10 @@
         <v>26</v>
       </c>
       <c r="B572" s="10">
-        <v>99.794100000000014</v>
+        <v>99.86410000000005</v>
       </c>
       <c r="C572" s="10">
-        <v>99.803900000000013</v>
+        <v>99.873899999999992</v>
       </c>
       <c r="D572" s="4"/>
     </row>
@@ -15358,10 +15358,10 @@
         <v>27</v>
       </c>
       <c r="B573" s="9">
-        <v>99.804000000000016</v>
+        <v>99.873999999999995</v>
       </c>
       <c r="C573" s="9">
-        <v>99.804000000000016</v>
+        <v>99.873999999999995</v>
       </c>
       <c r="D573" s="4"/>
     </row>
@@ -15370,10 +15370,10 @@
         <v>26</v>
       </c>
       <c r="B574" s="10">
-        <v>99.80410000000002</v>
+        <v>99.874099999999999</v>
       </c>
       <c r="C574" s="10">
-        <v>99.813900000000018</v>
+        <v>99.883899999999997</v>
       </c>
       <c r="D574" s="4"/>
     </row>
@@ -15382,10 +15382,10 @@
         <v>27</v>
       </c>
       <c r="B575" s="9">
-        <v>99.814000000000021</v>
+        <v>99.884</v>
       </c>
       <c r="C575" s="9">
-        <v>99.814000000000021</v>
+        <v>99.884</v>
       </c>
       <c r="D575" s="4"/>
     </row>
@@ -15394,10 +15394,10 @@
         <v>26</v>
       </c>
       <c r="B576" s="10">
-        <v>99.814100000000025</v>
+        <v>99.884100000000004</v>
       </c>
       <c r="C576" s="10">
-        <v>99.823900000000023</v>
+        <v>99.893900000000002</v>
       </c>
       <c r="D576" s="4"/>
     </row>
@@ -15406,10 +15406,10 @@
         <v>27</v>
       </c>
       <c r="B577" s="9">
-        <v>99.824000000000026</v>
+        <v>99.894000000000005</v>
       </c>
       <c r="C577" s="9">
-        <v>99.824000000000026</v>
+        <v>99.894000000000005</v>
       </c>
       <c r="D577" s="4"/>
     </row>
@@ -15418,10 +15418,10 @@
         <v>26</v>
       </c>
       <c r="B578" s="10">
-        <v>99.82410000000003</v>
+        <v>99.894100000000009</v>
       </c>
       <c r="C578" s="10">
-        <v>99.833900000000028</v>
+        <v>99.903899999999993</v>
       </c>
       <c r="D578" s="4"/>
     </row>
@@ -15430,10 +15430,10 @@
         <v>27</v>
       </c>
       <c r="B579" s="9">
-        <v>99.834000000000032</v>
+        <v>99.903999999999996</v>
       </c>
       <c r="C579" s="9">
-        <v>99.834000000000032</v>
+        <v>99.903999999999996</v>
       </c>
       <c r="D579" s="4"/>
     </row>
@@ -15442,10 +15442,10 @@
         <v>26</v>
       </c>
       <c r="B580" s="10">
-        <v>99.834100000000035</v>
+        <v>99.9041</v>
       </c>
       <c r="C580" s="10">
-        <v>99.843900000000033</v>
+        <v>99.913899999999998</v>
       </c>
       <c r="D580" s="4"/>
     </row>
@@ -15454,10 +15454,10 @@
         <v>27</v>
       </c>
       <c r="B581" s="9">
-        <v>99.844000000000037</v>
+        <v>99.914000000000001</v>
       </c>
       <c r="C581" s="9">
-        <v>99.844000000000037</v>
+        <v>99.914000000000001</v>
       </c>
       <c r="D581" s="4"/>
     </row>
@@ -15466,10 +15466,10 @@
         <v>26</v>
       </c>
       <c r="B582" s="10">
-        <v>99.84410000000004</v>
+        <v>99.914100000000005</v>
       </c>
       <c r="C582" s="10">
-        <v>99.853900000000039</v>
+        <v>99.919899999999998</v>
       </c>
       <c r="D582" s="4"/>
     </row>
@@ -15478,10 +15478,10 @@
         <v>27</v>
       </c>
       <c r="B583" s="9">
-        <v>99.854000000000042</v>
+        <v>99.92</v>
       </c>
       <c r="C583" s="9">
-        <v>99.854000000000042</v>
+        <v>99.92</v>
       </c>
       <c r="D583" s="4"/>
     </row>
@@ -15490,10 +15490,10 @@
         <v>26</v>
       </c>
       <c r="B584" s="10">
-        <v>99.854100000000045</v>
+        <v>99.920100000000005</v>
       </c>
       <c r="C584" s="10">
-        <v>99.863900000000044</v>
+        <v>99.926900000000003</v>
       </c>
       <c r="D584" s="4"/>
     </row>
@@ -15502,10 +15502,10 @@
         <v>27</v>
       </c>
       <c r="B585" s="9">
-        <v>99.864000000000047</v>
+        <v>99.927000000000007</v>
       </c>
       <c r="C585" s="9">
-        <v>99.864000000000047</v>
+        <v>99.927000000000007</v>
       </c>
       <c r="D585" s="4"/>
     </row>
@@ -15514,10 +15514,10 @@
         <v>26</v>
       </c>
       <c r="B586" s="10">
-        <v>99.86410000000005</v>
+        <v>99.92710000000001</v>
       </c>
       <c r="C586" s="10">
-        <v>99.873899999999992</v>
+        <v>99.927899999999994</v>
       </c>
       <c r="D586" s="4"/>
     </row>
@@ -15526,10 +15526,10 @@
         <v>27</v>
       </c>
       <c r="B587" s="9">
-        <v>99.873999999999995</v>
+        <v>99.927999999999997</v>
       </c>
       <c r="C587" s="9">
-        <v>99.873999999999995</v>
+        <v>99.927999999999997</v>
       </c>
       <c r="D587" s="4"/>
     </row>
@@ -15538,10 +15538,10 @@
         <v>26</v>
       </c>
       <c r="B588" s="10">
-        <v>99.874099999999999</v>
+        <v>99.928100000000001</v>
       </c>
       <c r="C588" s="10">
-        <v>99.883899999999997</v>
+        <v>99.928899999999999</v>
       </c>
       <c r="D588" s="4"/>
     </row>
@@ -15550,10 +15550,10 @@
         <v>27</v>
       </c>
       <c r="B589" s="9">
-        <v>99.884</v>
+        <v>99.929000000000002</v>
       </c>
       <c r="C589" s="9">
-        <v>99.884</v>
+        <v>99.929000000000002</v>
       </c>
       <c r="D589" s="4"/>
     </row>
@@ -15561,11 +15561,11 @@
       <c r="A590" t="s">
         <v>26</v>
       </c>
-      <c r="B590" s="10">
-        <v>99.884100000000004</v>
+      <c r="B590" s="9">
+        <v>99.929100000000005</v>
       </c>
       <c r="C590" s="10">
-        <v>99.893900000000002</v>
+        <v>99.929900000000004</v>
       </c>
       <c r="D590" s="4"/>
     </row>
@@ -15574,10 +15574,10 @@
         <v>27</v>
       </c>
       <c r="B591" s="9">
-        <v>99.894000000000005</v>
+        <v>99.93</v>
       </c>
       <c r="C591" s="9">
-        <v>99.894000000000005</v>
+        <v>99.93</v>
       </c>
       <c r="D591" s="4"/>
     </row>
@@ -15586,10 +15586,10 @@
         <v>26</v>
       </c>
       <c r="B592" s="10">
-        <v>99.894100000000009</v>
+        <v>99.93010000000001</v>
       </c>
       <c r="C592" s="10">
-        <v>99.903899999999993</v>
+        <v>99.939899999999994</v>
       </c>
       <c r="D592" s="4"/>
     </row>
@@ -15598,10 +15598,10 @@
         <v>27</v>
       </c>
       <c r="B593" s="9">
-        <v>99.903999999999996</v>
+        <v>99.94</v>
       </c>
       <c r="C593" s="9">
-        <v>99.903999999999996</v>
+        <v>99.94</v>
       </c>
       <c r="D593" s="4"/>
     </row>
@@ -15610,10 +15610,10 @@
         <v>26</v>
       </c>
       <c r="B594" s="10">
-        <v>99.9041</v>
+        <v>99.940100000000001</v>
       </c>
       <c r="C594" s="10">
-        <v>99.913899999999998</v>
+        <v>99.94189999999999</v>
       </c>
       <c r="D594" s="4"/>
     </row>
@@ -15622,344 +15622,330 @@
         <v>27</v>
       </c>
       <c r="B595" s="9">
-        <v>99.914000000000001</v>
+        <v>99.941999999999993</v>
       </c>
       <c r="C595" s="9">
-        <v>99.914000000000001</v>
+        <v>99.941999999999993</v>
       </c>
       <c r="D595" s="4"/>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A596" t="s">
-        <v>26</v>
+    <row r="596" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A596" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B596" s="10">
-        <v>99.914100000000005</v>
+        <v>99.942099999999996</v>
       </c>
       <c r="C596" s="10">
-        <v>99.919899999999998</v>
-      </c>
-      <c r="D596" s="4"/>
+        <v>100.11390000000002</v>
+      </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>27</v>
-      </c>
-      <c r="B597" s="9">
-        <v>99.92</v>
-      </c>
-      <c r="C597" s="9">
-        <v>99.92</v>
-      </c>
-      <c r="D597" s="4"/>
-    </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A598" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B597" s="10">
+        <v>100.114</v>
+      </c>
+      <c r="C597" s="10">
+        <v>100.26590000000002</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A598" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B598" s="10">
-        <v>99.920100000000005</v>
+        <v>100.26600000000001</v>
       </c>
       <c r="C598" s="10">
-        <v>99.926900000000003</v>
-      </c>
-      <c r="D598" s="4"/>
+        <v>100.30890000000001</v>
+      </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>27</v>
-      </c>
-      <c r="B599" s="9">
-        <v>99.927000000000007</v>
-      </c>
-      <c r="C599" s="9">
-        <v>99.927000000000007</v>
-      </c>
-      <c r="D599" s="4"/>
-    </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A600" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B599" s="10">
+        <v>100.309</v>
+      </c>
+      <c r="C599" s="10">
+        <v>100.4389</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A600" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B600" s="10">
-        <v>99.92710000000001</v>
+        <v>100.43899999999999</v>
       </c>
       <c r="C600" s="10">
-        <v>99.928899999999999</v>
-      </c>
-      <c r="D600" s="4"/>
+        <v>100.49690000000001</v>
+      </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>27</v>
-      </c>
-      <c r="B601" s="9">
-        <v>99.929000000000002</v>
-      </c>
-      <c r="C601" s="9">
-        <v>99.929000000000002</v>
-      </c>
-      <c r="D601" s="4"/>
-    </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A602" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B601" s="10">
+        <v>100.497</v>
+      </c>
+      <c r="C601" s="10">
+        <v>100.55090000000001</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A602" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B602" s="10">
-        <v>99.929100000000005</v>
+        <v>100.551</v>
       </c>
       <c r="C602" s="10">
-        <v>99.927899999999994</v>
-      </c>
-      <c r="D602" s="4"/>
+        <v>100.65190000000001</v>
+      </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>27</v>
-      </c>
-      <c r="B603" s="9">
-        <v>99.927999999999997</v>
-      </c>
-      <c r="C603" s="9">
-        <v>99.927999999999997</v>
-      </c>
-      <c r="D603" s="4"/>
-    </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A604" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B603" s="10">
+        <v>100.652</v>
+      </c>
+      <c r="C603" s="10">
+        <v>100.66690000000001</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A604" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B604" s="10">
-        <v>99.928100000000001</v>
+        <v>100.667</v>
       </c>
       <c r="C604" s="10">
-        <v>99.929900000000004</v>
-      </c>
-      <c r="D604" s="4"/>
+        <v>100.85190000000001</v>
+      </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>27</v>
-      </c>
-      <c r="B605" s="9">
-        <v>99.93</v>
-      </c>
-      <c r="C605" s="9">
-        <v>99.93</v>
-      </c>
-      <c r="D605" s="4"/>
-    </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A606" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B605" s="10">
+        <v>100.852</v>
+      </c>
+      <c r="C605" s="10">
+        <v>100.96790000000001</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A606" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B606" s="10">
-        <v>99.93010000000001</v>
+        <v>100.968</v>
       </c>
       <c r="C606" s="10">
-        <v>99.939899999999994</v>
-      </c>
-      <c r="D606" s="4"/>
+        <v>101.03290000000001</v>
+      </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>27</v>
-      </c>
-      <c r="B607" s="9">
-        <v>99.94</v>
-      </c>
-      <c r="C607" s="9">
-        <v>99.94</v>
-      </c>
-      <c r="D607" s="4"/>
-    </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A608" t="s">
-        <v>26</v>
+        <v>7</v>
+      </c>
+      <c r="B607" s="10">
+        <v>101.033</v>
+      </c>
+      <c r="C607" s="10">
+        <v>101.05090000000001</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A608" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B608" s="10">
-        <v>99.940100000000001</v>
+        <v>101.051</v>
       </c>
       <c r="C608" s="10">
-        <v>99.94189999999999</v>
-      </c>
-      <c r="D608" s="4"/>
-    </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.35">
+        <v>101.13590000000001</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>27</v>
-      </c>
-      <c r="B609" s="9">
-        <v>99.941999999999993</v>
-      </c>
-      <c r="C609" s="9">
-        <v>99.941999999999993</v>
-      </c>
-      <c r="D609" s="4"/>
-    </row>
-    <row r="610" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="B609" s="10">
+        <v>101.136</v>
+      </c>
+      <c r="C609" s="10">
+        <v>101.85590000000001</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A610" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B610" s="10">
-        <v>99.942099999999996</v>
+        <v>101.85599999999999</v>
       </c>
       <c r="C610" s="10">
-        <v>100.11390000000002</v>
-      </c>
-    </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.35">
+        <v>102.44690000000001</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>7</v>
       </c>
       <c r="B611" s="10">
-        <v>100.114</v>
+        <v>102.447</v>
       </c>
       <c r="C611" s="10">
-        <v>100.26590000000002</v>
-      </c>
-    </row>
-    <row r="612" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>102.65690000000001</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A612" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B612" s="10">
-        <v>100.26600000000001</v>
+        <v>102.657</v>
       </c>
       <c r="C612" s="10">
-        <v>100.30890000000001</v>
-      </c>
-    </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.35">
+        <v>103.43390000000001</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>7</v>
       </c>
       <c r="B613" s="10">
-        <v>100.309</v>
+        <v>103.434</v>
       </c>
       <c r="C613" s="10">
-        <v>100.4389</v>
-      </c>
-    </row>
-    <row r="614" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>104.04790000000001</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A614" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B614" s="10">
-        <v>100.43899999999999</v>
+        <v>104.048</v>
       </c>
       <c r="C614" s="10">
-        <v>100.49690000000001</v>
-      </c>
-    </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104.64990000000002</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>7</v>
       </c>
       <c r="B615" s="10">
-        <v>100.497</v>
+        <v>104.65</v>
       </c>
       <c r="C615" s="10">
-        <v>100.55090000000001</v>
-      </c>
-    </row>
-    <row r="616" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>104.91190000000002</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A616" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B616" s="10">
-        <v>100.551</v>
+        <v>104.91200000000001</v>
       </c>
       <c r="C616" s="10">
-        <v>100.65190000000001</v>
-      </c>
-    </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.35">
+        <v>105.63890000000001</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>7</v>
       </c>
       <c r="B617" s="10">
-        <v>100.652</v>
+        <v>105.639</v>
       </c>
       <c r="C617" s="10">
-        <v>100.66690000000001</v>
-      </c>
-    </row>
-    <row r="618" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>106.00890000000001</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A618" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B618" s="10">
-        <v>100.667</v>
+        <v>106.009</v>
       </c>
       <c r="C618" s="10">
-        <v>100.85190000000001</v>
-      </c>
-    </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.35">
+        <v>106.34590000000001</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>7</v>
       </c>
       <c r="B619" s="10">
-        <v>100.852</v>
+        <v>106.346</v>
       </c>
       <c r="C619" s="10">
-        <v>100.96790000000001</v>
-      </c>
-    </row>
-    <row r="620" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>106.68790000000001</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A620" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B620" s="10">
-        <v>100.968</v>
+        <v>106.688</v>
       </c>
       <c r="C620" s="10">
-        <v>101.03290000000001</v>
-      </c>
-    </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.35">
+        <v>106.74290000000001</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>7</v>
       </c>
       <c r="B621" s="10">
-        <v>101.033</v>
+        <v>106.74299999999999</v>
       </c>
       <c r="C621" s="10">
-        <v>101.05090000000001</v>
-      </c>
-    </row>
-    <row r="622" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>106.9329</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A622" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B622" s="10">
-        <v>101.051</v>
+        <v>106.93299999999999</v>
       </c>
       <c r="C622" s="10">
-        <v>101.13590000000001</v>
-      </c>
-    </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.35">
+        <v>107.24790000000002</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>7</v>
       </c>
       <c r="B623" s="10">
-        <v>101.136</v>
+        <v>107.248</v>
       </c>
       <c r="C623" s="10">
-        <v>101.85590000000001</v>
-      </c>
-    </row>
-    <row r="624" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+        <v>107.28690000000002</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A624" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B624" s="10">
-        <v>101.85599999999999</v>
+        <v>107.28700000000001</v>
       </c>
       <c r="C624" s="10">
-        <v>102.44690000000001</v>
+        <v>107.37890000000002</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.35">
@@ -15967,10 +15953,10 @@
         <v>7</v>
       </c>
       <c r="B625" s="10">
-        <v>102.447</v>
+        <v>107.379</v>
       </c>
       <c r="C625" s="10">
-        <v>102.65690000000001</v>
+        <v>107.56290000000001</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -15978,10 +15964,10 @@
         <v>13</v>
       </c>
       <c r="B626" s="10">
-        <v>102.657</v>
+        <v>107.563</v>
       </c>
       <c r="C626" s="10">
-        <v>103.43390000000001</v>
+        <v>108.17890000000001</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.35">
@@ -15989,10 +15975,10 @@
         <v>7</v>
       </c>
       <c r="B627" s="10">
-        <v>103.434</v>
+        <v>108.179</v>
       </c>
       <c r="C627" s="10">
-        <v>104.04790000000001</v>
+        <v>108.27790000000002</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16000,10 +15986,10 @@
         <v>13</v>
       </c>
       <c r="B628" s="10">
-        <v>104.048</v>
+        <v>108.27800000000001</v>
       </c>
       <c r="C628" s="10">
-        <v>104.64990000000002</v>
+        <v>108.45590000000001</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.35">
@@ -16011,10 +15997,10 @@
         <v>7</v>
       </c>
       <c r="B629" s="10">
-        <v>104.65</v>
+        <v>108.456</v>
       </c>
       <c r="C629" s="10">
-        <v>104.91190000000002</v>
+        <v>108.97290000000001</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16022,10 +16008,10 @@
         <v>13</v>
       </c>
       <c r="B630" s="10">
-        <v>104.91200000000001</v>
+        <v>108.973</v>
       </c>
       <c r="C630" s="10">
-        <v>105.63890000000001</v>
+        <v>109.52690000000001</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.35">
@@ -16033,10 +16019,10 @@
         <v>7</v>
       </c>
       <c r="B631" s="10">
-        <v>105.639</v>
+        <v>109.527</v>
       </c>
       <c r="C631" s="10">
-        <v>106.00890000000001</v>
+        <v>109.57790000000001</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16044,10 +16030,10 @@
         <v>13</v>
       </c>
       <c r="B632" s="10">
-        <v>106.009</v>
+        <v>109.578</v>
       </c>
       <c r="C632" s="10">
-        <v>106.34590000000001</v>
+        <v>109.83090000000001</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.35">
@@ -16055,10 +16041,10 @@
         <v>7</v>
       </c>
       <c r="B633" s="10">
-        <v>106.346</v>
+        <v>109.831</v>
       </c>
       <c r="C633" s="10">
-        <v>106.68790000000001</v>
+        <v>110.14790000000001</v>
       </c>
     </row>
     <row r="634" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16066,10 +16052,10 @@
         <v>13</v>
       </c>
       <c r="B634" s="10">
-        <v>106.688</v>
+        <v>110.148</v>
       </c>
       <c r="C634" s="10">
-        <v>106.74290000000001</v>
+        <v>110.39990000000002</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.35">
@@ -16077,10 +16063,10 @@
         <v>7</v>
       </c>
       <c r="B635" s="10">
-        <v>106.74299999999999</v>
+        <v>110.4</v>
       </c>
       <c r="C635" s="10">
-        <v>106.9329</v>
+        <v>110.61590000000001</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16088,10 +16074,10 @@
         <v>13</v>
       </c>
       <c r="B636" s="10">
-        <v>106.93299999999999</v>
+        <v>110.616</v>
       </c>
       <c r="C636" s="10">
-        <v>107.24790000000002</v>
+        <v>110.76190000000001</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.35">
@@ -16099,10 +16085,10 @@
         <v>7</v>
       </c>
       <c r="B637" s="10">
-        <v>107.248</v>
+        <v>110.762</v>
       </c>
       <c r="C637" s="10">
-        <v>107.28690000000002</v>
+        <v>110.81290000000001</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16110,10 +16096,10 @@
         <v>13</v>
       </c>
       <c r="B638" s="10">
-        <v>107.28700000000001</v>
+        <v>110.813</v>
       </c>
       <c r="C638" s="10">
-        <v>107.37890000000002</v>
+        <v>110.9689</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.35">
@@ -16121,10 +16107,10 @@
         <v>7</v>
       </c>
       <c r="B639" s="10">
-        <v>107.379</v>
+        <v>110.96899999999999</v>
       </c>
       <c r="C639" s="10">
-        <v>107.56290000000001</v>
+        <v>111.15390000000001</v>
       </c>
     </row>
     <row r="640" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16132,10 +16118,10 @@
         <v>13</v>
       </c>
       <c r="B640" s="10">
-        <v>107.563</v>
+        <v>111.154</v>
       </c>
       <c r="C640" s="10">
-        <v>108.17890000000001</v>
+        <v>111.19390000000001</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.35">
@@ -16143,10 +16129,10 @@
         <v>7</v>
       </c>
       <c r="B641" s="10">
-        <v>108.179</v>
+        <v>111.194</v>
       </c>
       <c r="C641" s="10">
-        <v>108.27790000000002</v>
+        <v>111.40790000000001</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16154,10 +16140,10 @@
         <v>13</v>
       </c>
       <c r="B642" s="10">
-        <v>108.27800000000001</v>
+        <v>111.408</v>
       </c>
       <c r="C642" s="10">
-        <v>108.45590000000001</v>
+        <v>111.73890000000002</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.35">
@@ -16165,10 +16151,10 @@
         <v>7</v>
       </c>
       <c r="B643" s="10">
-        <v>108.456</v>
+        <v>111.739</v>
       </c>
       <c r="C643" s="10">
-        <v>108.97290000000001</v>
+        <v>111.93990000000001</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16176,10 +16162,10 @@
         <v>13</v>
       </c>
       <c r="B644" s="10">
-        <v>108.973</v>
+        <v>111.94</v>
       </c>
       <c r="C644" s="10">
-        <v>109.52690000000001</v>
+        <v>112.70790000000001</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.35">
@@ -16187,10 +16173,10 @@
         <v>7</v>
       </c>
       <c r="B645" s="10">
-        <v>109.527</v>
+        <v>112.708</v>
       </c>
       <c r="C645" s="10">
-        <v>109.57790000000001</v>
+        <v>113.07890000000002</v>
       </c>
     </row>
     <row r="646" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16198,10 +16184,10 @@
         <v>13</v>
       </c>
       <c r="B646" s="10">
-        <v>109.578</v>
+        <v>113.07900000000001</v>
       </c>
       <c r="C646" s="10">
-        <v>109.83090000000001</v>
+        <v>113.88590000000001</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.35">
@@ -16209,10 +16195,10 @@
         <v>7</v>
       </c>
       <c r="B647" s="10">
-        <v>109.831</v>
+        <v>113.886</v>
       </c>
       <c r="C647" s="10">
-        <v>110.14790000000001</v>
+        <v>114.11890000000001</v>
       </c>
     </row>
     <row r="648" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16220,10 +16206,10 @@
         <v>13</v>
       </c>
       <c r="B648" s="10">
-        <v>110.148</v>
+        <v>114.119</v>
       </c>
       <c r="C648" s="10">
-        <v>110.39990000000002</v>
+        <v>114.27690000000001</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.35">
@@ -16231,10 +16217,10 @@
         <v>7</v>
       </c>
       <c r="B649" s="10">
-        <v>110.4</v>
+        <v>114.277</v>
       </c>
       <c r="C649" s="10">
-        <v>110.61590000000001</v>
+        <v>114.36990000000002</v>
       </c>
     </row>
     <row r="650" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16242,10 +16228,10 @@
         <v>13</v>
       </c>
       <c r="B650" s="10">
-        <v>110.616</v>
+        <v>114.37</v>
       </c>
       <c r="C650" s="10">
-        <v>110.76190000000001</v>
+        <v>114.47690000000001</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.35">
@@ -16253,10 +16239,10 @@
         <v>7</v>
       </c>
       <c r="B651" s="10">
-        <v>110.762</v>
+        <v>114.477</v>
       </c>
       <c r="C651" s="10">
-        <v>110.81290000000001</v>
+        <v>114.52090000000001</v>
       </c>
     </row>
     <row r="652" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16264,10 +16250,10 @@
         <v>13</v>
       </c>
       <c r="B652" s="10">
-        <v>110.813</v>
+        <v>114.521</v>
       </c>
       <c r="C652" s="10">
-        <v>110.9689</v>
+        <v>114.61090000000002</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.35">
@@ -16275,10 +16261,10 @@
         <v>7</v>
       </c>
       <c r="B653" s="10">
-        <v>110.96899999999999</v>
+        <v>114.611</v>
       </c>
       <c r="C653" s="10">
-        <v>111.15390000000001</v>
+        <v>115.10190000000001</v>
       </c>
     </row>
     <row r="654" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
@@ -16286,10 +16272,10 @@
         <v>13</v>
       </c>
       <c r="B654" s="10">
-        <v>111.154</v>
+        <v>115.102</v>
       </c>
       <c r="C654" s="10">
-        <v>111.19390000000001</v>
+        <v>115.31490000000001</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.35">
@@ -16297,168 +16283,14 @@
         <v>7</v>
       </c>
       <c r="B655" s="10">
-        <v>111.194</v>
+        <v>115.315</v>
       </c>
       <c r="C655" s="10">
-        <v>111.40790000000001</v>
+        <v>116</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A656" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B656" s="10">
-        <v>111.408</v>
-      </c>
-      <c r="C656" s="10">
-        <v>111.73890000000002</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A657" t="s">
-        <v>7</v>
-      </c>
-      <c r="B657" s="10">
-        <v>111.739</v>
-      </c>
-      <c r="C657" s="10">
-        <v>111.93990000000001</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A658" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B658" s="10">
-        <v>111.94</v>
-      </c>
-      <c r="C658" s="10">
-        <v>112.70790000000001</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A659" t="s">
-        <v>7</v>
-      </c>
-      <c r="B659" s="10">
-        <v>112.708</v>
-      </c>
-      <c r="C659" s="10">
-        <v>113.07890000000002</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A660" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B660" s="10">
-        <v>113.07900000000001</v>
-      </c>
-      <c r="C660" s="10">
-        <v>113.88590000000001</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A661" t="s">
-        <v>7</v>
-      </c>
-      <c r="B661" s="10">
-        <v>113.886</v>
-      </c>
-      <c r="C661" s="10">
-        <v>114.11890000000001</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A662" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B662" s="10">
-        <v>114.119</v>
-      </c>
-      <c r="C662" s="10">
-        <v>114.27690000000001</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A663" t="s">
-        <v>7</v>
-      </c>
-      <c r="B663" s="10">
-        <v>114.277</v>
-      </c>
-      <c r="C663" s="10">
-        <v>114.36990000000002</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A664" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B664" s="10">
-        <v>114.37</v>
-      </c>
-      <c r="C664" s="10">
-        <v>114.47690000000001</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A665" t="s">
-        <v>7</v>
-      </c>
-      <c r="B665" s="10">
-        <v>114.477</v>
-      </c>
-      <c r="C665" s="10">
-        <v>114.52090000000001</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A666" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B666" s="10">
-        <v>114.521</v>
-      </c>
-      <c r="C666" s="10">
-        <v>114.61090000000002</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A667" t="s">
-        <v>7</v>
-      </c>
-      <c r="B667" s="10">
-        <v>114.611</v>
-      </c>
-      <c r="C667" s="10">
-        <v>115.10190000000001</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A668" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B668" s="10">
-        <v>115.102</v>
-      </c>
-      <c r="C668" s="10">
-        <v>115.31490000000001</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A669" t="s">
-        <v>7</v>
-      </c>
-      <c r="B669" s="10">
-        <v>115.315</v>
-      </c>
-      <c r="C669" s="10">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A670" s="7"/>
+      <c r="A656" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16878,7 +16710,24 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{417B8DC7-4BAF-4B78-A575-E534128B7FCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{417B8DC7-4BAF-4B78-A575-E534128B7FCE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16890,7 +16739,11 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D107E374-131C-4957-8BB3-E4DC3CDB3021}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D107E374-131C-4957-8BB3-E4DC3CDB3021}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16901,6 +16754,8 @@
     <ds:schemaRef ds:uri="c32bb4e5-d30f-47c7-b40d-8e40c9a47274"/>
     <ds:schemaRef ds:uri="9ecf1a6e-3aad-4311-93bc-48574f90e2b0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v4"/>
+    <ds:schemaRef ds:uri="a4282dde-c91e-40c5-9bfe-d2af68f8b118"/>
+    <ds:schemaRef ds:uri="f57c62ac-5b60-40b7-9460-0473ac1a050a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>